--- a/product_selector_out/STM32MP2 series.xlsx
+++ b/product_selector_out/STM32MP2 series.xlsx
@@ -61,12 +61,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFEB9C"/>
+        <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
+        <fgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
   </fills>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="BC12" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32mp211a.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -1461,7 +1461,7 @@
       </c>
       <c r="BC13" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32mp211c.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="BC14" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32mp211a.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="BC15" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32mp211c.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2292,7 +2292,7 @@
       </c>
       <c r="BC16" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32mp251c.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2569,7 +2569,7 @@
       </c>
       <c r="BC17" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32mp251a.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2846,7 +2846,7 @@
       </c>
       <c r="BC18" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32mp251c.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -3123,7 +3123,7 @@
       </c>
       <c r="BC19" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32mp251a.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="BC22" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32mp251a.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -4231,7 +4231,7 @@
       </c>
       <c r="BC23" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32mp251c.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -4508,7 +4508,7 @@
       </c>
       <c r="BC24" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32mp251c.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -4785,7 +4785,7 @@
       </c>
       <c r="BC25" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32mp251a.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -5062,7 +5062,7 @@
       </c>
       <c r="BC26" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32mp251c.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -5339,7 +5339,7 @@
       </c>
       <c r="BC27" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32mp251a.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -5616,7 +5616,7 @@
       </c>
       <c r="BC28" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32mp231c.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="BC29" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32mp231a.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -6170,7 +6170,7 @@
       </c>
       <c r="BC30" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32mp231a.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -6447,7 +6447,7 @@
       </c>
       <c r="BC31" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32mp231c.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -7001,7 +7001,7 @@
       </c>
       <c r="BC33" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32mp211c.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -7555,7 +7555,7 @@
       </c>
       <c r="BC35" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32mp211a.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -7832,7 +7832,7 @@
       </c>
       <c r="BC36" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32mp231c.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -8109,7 +8109,7 @@
       </c>
       <c r="BC37" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32mp231a.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -8940,7 +8940,7 @@
       </c>
       <c r="BC40" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32mp231c.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -9217,7 +9217,7 @@
       </c>
       <c r="BC41" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32mp231c.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -9494,7 +9494,7 @@
       </c>
       <c r="BC42" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32mp231a.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -9771,7 +9771,7 @@
       </c>
       <c r="BC43" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32mp231a.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -10048,7 +10048,7 @@
       </c>
       <c r="BC44" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32mp211c.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -10325,7 +10325,7 @@
       </c>
       <c r="BC45" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32mp211c.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -10602,7 +10602,7 @@
       </c>
       <c r="BC46" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32mp211a.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -10879,7 +10879,7 @@
       </c>
       <c r="BC47" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32mp211a.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -11156,7 +11156,7 @@
       </c>
       <c r="BC48" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32mp251a.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -11433,7 +11433,7 @@
       </c>
       <c r="BC49" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32mp251c.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -11710,7 +11710,7 @@
       </c>
       <c r="BC50" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32mp251a.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -11987,7 +11987,7 @@
       </c>
       <c r="BC51" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32mp251c.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -12541,14 +12541,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F12" s="6" t="inlineStr">
@@ -12606,7 +12606,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Q12" s="8" t="inlineStr">
+      <c r="Q12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12626,7 +12626,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U12" s="8" t="inlineStr">
+      <c r="U12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12641,7 +12641,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="X12" s="8" t="inlineStr">
+      <c r="X12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12676,12 +12676,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF12" s="8" t="inlineStr">
+      <c r="AE12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12696,19 +12696,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AJ12" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AK12" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AI12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AJ12" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AK12" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AL12" s="6" t="inlineStr">
@@ -12726,12 +12726,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AO12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AP12" s="8" t="inlineStr">
+      <c r="AO12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AP12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12761,7 +12761,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AV12" s="8" t="inlineStr">
+      <c r="AV12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12771,34 +12771,34 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AY12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AZ12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BA12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BB12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BC12" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AX12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AY12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AZ12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BA12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BB12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BC12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -12818,14 +12818,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D13" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="E13" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
@@ -12883,7 +12883,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Q13" s="8" t="inlineStr">
+      <c r="Q13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12903,7 +12903,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U13" s="8" t="inlineStr">
+      <c r="U13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12918,7 +12918,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="X13" s="8" t="inlineStr">
+      <c r="X13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12953,12 +12953,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF13" s="8" t="inlineStr">
+      <c r="AE13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12973,19 +12973,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AJ13" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AK13" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AI13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AJ13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AK13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AL13" s="6" t="inlineStr">
@@ -13038,7 +13038,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AV13" s="8" t="inlineStr">
+      <c r="AV13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13048,17 +13048,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AY13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AZ13" s="8" t="inlineStr">
+      <c r="AX13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AY13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AZ13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13073,9 +13073,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BC13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -13095,14 +13095,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D14" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="E14" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
@@ -13160,7 +13160,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Q14" s="8" t="inlineStr">
+      <c r="Q14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13180,7 +13180,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U14" s="8" t="inlineStr">
+      <c r="U14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13195,7 +13195,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="X14" s="8" t="inlineStr">
+      <c r="X14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13230,12 +13230,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF14" s="8" t="inlineStr">
+      <c r="AE14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13250,19 +13250,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AJ14" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AK14" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AI14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AJ14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AK14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AL14" s="6" t="inlineStr">
@@ -13280,12 +13280,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AO14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AP14" s="8" t="inlineStr">
+      <c r="AO14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AP14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13315,7 +13315,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AV14" s="8" t="inlineStr">
+      <c r="AV14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13325,17 +13325,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AY14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AZ14" s="8" t="inlineStr">
+      <c r="AX14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AY14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AZ14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13350,9 +13350,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BC14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -13372,14 +13372,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="E15" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
@@ -13437,7 +13437,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Q15" s="8" t="inlineStr">
+      <c r="Q15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13457,7 +13457,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U15" s="8" t="inlineStr">
+      <c r="U15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13472,7 +13472,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="X15" s="8" t="inlineStr">
+      <c r="X15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13507,12 +13507,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF15" s="8" t="inlineStr">
+      <c r="AE15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13527,19 +13527,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AJ15" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AK15" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AI15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AJ15" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AK15" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AL15" s="6" t="inlineStr">
@@ -13592,7 +13592,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AV15" s="8" t="inlineStr">
+      <c r="AV15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13602,17 +13602,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AY15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AZ15" s="8" t="inlineStr">
+      <c r="AX15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AY15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AZ15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13627,9 +13627,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BC15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -13654,9 +13654,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E16" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr">
@@ -13734,7 +13734,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U16" s="8" t="inlineStr">
+      <c r="U16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13754,12 +13754,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Y16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z16" s="8" t="inlineStr">
+      <c r="Y16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13784,12 +13784,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF16" s="8" t="inlineStr">
+      <c r="AE16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13804,19 +13804,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI16" s="8" t="inlineStr">
+      <c r="AI16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AJ16" s="7" t="inlineStr">
         <is>
-          <t>AMBIGUOUS</t>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AK16" s="7" t="inlineStr">
         <is>
-          <t>AMBIGUOUS</t>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AL16" s="6" t="inlineStr">
@@ -13869,7 +13869,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AV16" s="8" t="inlineStr">
+      <c r="AV16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13879,17 +13879,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AY16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AZ16" s="8" t="inlineStr">
+      <c r="AX16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AY16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AZ16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13904,9 +13904,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BC16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -13931,9 +13931,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E17" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
@@ -14011,7 +14011,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U17" s="8" t="inlineStr">
+      <c r="U17" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -14031,12 +14031,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Y17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z17" s="8" t="inlineStr">
+      <c r="Y17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z17" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -14061,12 +14061,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF17" s="8" t="inlineStr">
+      <c r="AE17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF17" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -14081,19 +14081,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI17" s="8" t="inlineStr">
+      <c r="AI17" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AJ17" s="7" t="inlineStr">
         <is>
-          <t>AMBIGUOUS</t>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AK17" s="7" t="inlineStr">
         <is>
-          <t>AMBIGUOUS</t>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AL17" s="6" t="inlineStr">
@@ -14111,12 +14111,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AO17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AP17" s="8" t="inlineStr">
+      <c r="AO17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AP17" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -14146,7 +14146,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AV17" s="8" t="inlineStr">
+      <c r="AV17" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -14156,17 +14156,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AY17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AZ17" s="8" t="inlineStr">
+      <c r="AX17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AY17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AZ17" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -14181,9 +14181,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC17" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BC17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -14208,9 +14208,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E18" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F18" s="6" t="inlineStr">
@@ -14288,7 +14288,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U18" s="8" t="inlineStr">
+      <c r="U18" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -14308,12 +14308,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Y18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z18" s="8" t="inlineStr">
+      <c r="Y18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z18" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -14338,12 +14338,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF18" s="8" t="inlineStr">
+      <c r="AE18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF18" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -14358,19 +14358,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI18" s="8" t="inlineStr">
+      <c r="AI18" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AJ18" s="7" t="inlineStr">
         <is>
-          <t>AMBIGUOUS</t>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AK18" s="7" t="inlineStr">
         <is>
-          <t>AMBIGUOUS</t>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AL18" s="6" t="inlineStr">
@@ -14423,7 +14423,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AV18" s="8" t="inlineStr">
+      <c r="AV18" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -14433,17 +14433,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AY18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AZ18" s="8" t="inlineStr">
+      <c r="AX18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AY18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AZ18" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -14458,9 +14458,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC18" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BC18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -14485,9 +14485,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E19" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
@@ -14565,7 +14565,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U19" s="8" t="inlineStr">
+      <c r="U19" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -14585,12 +14585,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Y19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z19" s="8" t="inlineStr">
+      <c r="Y19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z19" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -14615,12 +14615,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF19" s="8" t="inlineStr">
+      <c r="AE19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF19" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -14635,19 +14635,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI19" s="8" t="inlineStr">
+      <c r="AI19" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AJ19" s="7" t="inlineStr">
         <is>
-          <t>AMBIGUOUS</t>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AK19" s="7" t="inlineStr">
         <is>
-          <t>AMBIGUOUS</t>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AL19" s="6" t="inlineStr">
@@ -14665,12 +14665,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AO19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AP19" s="8" t="inlineStr">
+      <c r="AO19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AP19" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -14700,7 +14700,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AV19" s="8" t="inlineStr">
+      <c r="AV19" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -14710,17 +14710,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AY19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AZ19" s="8" t="inlineStr">
+      <c r="AX19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AY19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AZ19" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -14735,9 +14735,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC19" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BC19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -14762,7 +14762,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E20" s="7" t="inlineStr">
+      <c r="E20" s="8" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
@@ -14822,7 +14822,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Q20" s="8" t="inlineStr">
+      <c r="Q20" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -14842,12 +14842,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="V20" s="8" t="inlineStr">
+      <c r="U20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="V20" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -14862,12 +14862,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Y20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z20" s="8" t="inlineStr">
+      <c r="Y20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z20" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -14892,12 +14892,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF20" s="8" t="inlineStr">
+      <c r="AE20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF20" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -14912,17 +14912,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AJ20" s="7" t="inlineStr">
+      <c r="AI20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AJ20" s="8" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AK20" s="7" t="inlineStr">
+      <c r="AK20" s="8" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
@@ -14942,12 +14942,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AO20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AP20" s="8" t="inlineStr">
+      <c r="AO20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AP20" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -14977,7 +14977,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AV20" s="8" t="inlineStr">
+      <c r="AV20" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -14987,17 +14987,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AY20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AZ20" s="8" t="inlineStr">
+      <c r="AX20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AY20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AZ20" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -15039,7 +15039,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E21" s="7" t="inlineStr">
+      <c r="E21" s="8" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
@@ -15099,7 +15099,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Q21" s="8" t="inlineStr">
+      <c r="Q21" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -15119,12 +15119,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="V21" s="8" t="inlineStr">
+      <c r="U21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="V21" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -15139,12 +15139,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Y21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z21" s="8" t="inlineStr">
+      <c r="Y21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z21" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -15169,12 +15169,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF21" s="8" t="inlineStr">
+      <c r="AE21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF21" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -15189,17 +15189,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AJ21" s="7" t="inlineStr">
+      <c r="AI21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AJ21" s="8" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AK21" s="7" t="inlineStr">
+      <c r="AK21" s="8" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
@@ -15254,7 +15254,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AV21" s="8" t="inlineStr">
+      <c r="AV21" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -15264,17 +15264,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AY21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AZ21" s="8" t="inlineStr">
+      <c r="AX21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AY21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AZ21" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -15316,9 +15316,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E22" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr">
@@ -15376,7 +15376,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Q22" s="8" t="inlineStr">
+      <c r="Q22" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -15396,12 +15396,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="V22" s="8" t="inlineStr">
+      <c r="U22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="V22" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -15416,12 +15416,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Y22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z22" s="8" t="inlineStr">
+      <c r="Y22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z22" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -15446,12 +15446,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF22" s="8" t="inlineStr">
+      <c r="AE22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF22" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -15466,19 +15466,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI22" s="8" t="inlineStr">
+      <c r="AI22" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AJ22" s="7" t="inlineStr">
         <is>
-          <t>AMBIGUOUS</t>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AK22" s="7" t="inlineStr">
         <is>
-          <t>AMBIGUOUS</t>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AL22" s="6" t="inlineStr">
@@ -15496,12 +15496,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AO22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AP22" s="8" t="inlineStr">
+      <c r="AO22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AP22" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -15531,7 +15531,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AV22" s="8" t="inlineStr">
+      <c r="AV22" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -15541,17 +15541,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AY22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AZ22" s="8" t="inlineStr">
+      <c r="AX22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AY22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AZ22" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -15566,9 +15566,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC22" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BC22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -15593,9 +15593,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E23" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
@@ -15653,7 +15653,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Q23" s="8" t="inlineStr">
+      <c r="Q23" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -15673,12 +15673,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="V23" s="8" t="inlineStr">
+      <c r="U23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="V23" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -15693,12 +15693,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Y23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z23" s="8" t="inlineStr">
+      <c r="Y23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z23" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -15723,12 +15723,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF23" s="8" t="inlineStr">
+      <c r="AE23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF23" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -15743,19 +15743,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI23" s="8" t="inlineStr">
+      <c r="AI23" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AJ23" s="7" t="inlineStr">
         <is>
-          <t>AMBIGUOUS</t>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AK23" s="7" t="inlineStr">
         <is>
-          <t>AMBIGUOUS</t>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AL23" s="6" t="inlineStr">
@@ -15808,7 +15808,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AV23" s="8" t="inlineStr">
+      <c r="AV23" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -15818,17 +15818,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AY23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AZ23" s="8" t="inlineStr">
+      <c r="AX23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AY23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AZ23" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -15843,9 +15843,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BC23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -15870,9 +15870,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E24" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F24" s="6" t="inlineStr">
@@ -15930,7 +15930,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Q24" s="8" t="inlineStr">
+      <c r="Q24" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -15950,7 +15950,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U24" s="8" t="inlineStr">
+      <c r="U24" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -15960,7 +15960,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W24" s="8" t="inlineStr">
+      <c r="W24" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -15975,7 +15975,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Z24" s="8" t="inlineStr">
+      <c r="Z24" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -16000,12 +16000,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE24" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF24" s="8" t="inlineStr">
+      <c r="AE24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF24" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -16020,19 +16020,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI24" s="8" t="inlineStr">
+      <c r="AI24" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AJ24" s="7" t="inlineStr">
         <is>
-          <t>AMBIGUOUS</t>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AK24" s="7" t="inlineStr">
         <is>
-          <t>AMBIGUOUS</t>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AL24" s="6" t="inlineStr">
@@ -16085,7 +16085,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AV24" s="8" t="inlineStr">
+      <c r="AV24" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -16095,17 +16095,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX24" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AY24" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AZ24" s="8" t="inlineStr">
+      <c r="AX24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AY24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AZ24" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -16120,9 +16120,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC24" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BC24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -16147,9 +16147,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E25" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F25" s="6" t="inlineStr">
@@ -16207,7 +16207,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Q25" s="8" t="inlineStr">
+      <c r="Q25" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -16227,7 +16227,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U25" s="8" t="inlineStr">
+      <c r="U25" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -16247,12 +16247,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Y25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z25" s="8" t="inlineStr">
+      <c r="Y25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z25" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -16277,12 +16277,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF25" s="8" t="inlineStr">
+      <c r="AE25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF25" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -16297,19 +16297,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI25" s="8" t="inlineStr">
+      <c r="AI25" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AJ25" s="7" t="inlineStr">
         <is>
-          <t>AMBIGUOUS</t>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AK25" s="7" t="inlineStr">
         <is>
-          <t>AMBIGUOUS</t>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AL25" s="6" t="inlineStr">
@@ -16327,12 +16327,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AO25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AP25" s="8" t="inlineStr">
+      <c r="AO25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AP25" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -16362,7 +16362,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AV25" s="8" t="inlineStr">
+      <c r="AV25" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -16372,17 +16372,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AY25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AZ25" s="8" t="inlineStr">
+      <c r="AX25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AY25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AZ25" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -16397,9 +16397,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC25" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BC25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -16424,9 +16424,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E26" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F26" s="6" t="inlineStr">
@@ -16484,7 +16484,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Q26" s="8" t="inlineStr">
+      <c r="Q26" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -16504,7 +16504,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U26" s="8" t="inlineStr">
+      <c r="U26" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -16524,12 +16524,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Y26" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z26" s="8" t="inlineStr">
+      <c r="Y26" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z26" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -16554,12 +16554,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE26" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF26" s="8" t="inlineStr">
+      <c r="AE26" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF26" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -16574,19 +16574,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI26" s="8" t="inlineStr">
+      <c r="AI26" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AJ26" s="7" t="inlineStr">
         <is>
-          <t>AMBIGUOUS</t>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AK26" s="7" t="inlineStr">
         <is>
-          <t>AMBIGUOUS</t>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AL26" s="6" t="inlineStr">
@@ -16639,7 +16639,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AV26" s="8" t="inlineStr">
+      <c r="AV26" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -16649,17 +16649,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX26" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AY26" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AZ26" s="8" t="inlineStr">
+      <c r="AX26" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AY26" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AZ26" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -16674,9 +16674,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC26" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BC26" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -16701,9 +16701,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E27" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F27" s="6" t="inlineStr">
@@ -16761,7 +16761,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Q27" s="8" t="inlineStr">
+      <c r="Q27" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -16781,7 +16781,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U27" s="8" t="inlineStr">
+      <c r="U27" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -16801,12 +16801,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Y27" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z27" s="8" t="inlineStr">
+      <c r="Y27" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z27" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -16831,12 +16831,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE27" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF27" s="8" t="inlineStr">
+      <c r="AE27" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF27" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -16851,19 +16851,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI27" s="8" t="inlineStr">
+      <c r="AI27" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AJ27" s="7" t="inlineStr">
         <is>
-          <t>AMBIGUOUS</t>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AK27" s="7" t="inlineStr">
         <is>
-          <t>AMBIGUOUS</t>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AL27" s="6" t="inlineStr">
@@ -16881,12 +16881,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AO27" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AP27" s="8" t="inlineStr">
+      <c r="AO27" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AP27" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -16916,7 +16916,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AV27" s="8" t="inlineStr">
+      <c r="AV27" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -16926,17 +16926,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX27" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AY27" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AZ27" s="8" t="inlineStr">
+      <c r="AX27" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AY27" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AZ27" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -16951,9 +16951,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC27" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BC27" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -16978,9 +16978,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E28" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="E28" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F28" s="6" t="inlineStr">
@@ -17058,7 +17058,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U28" s="8" t="inlineStr">
+      <c r="U28" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -17073,7 +17073,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="X28" s="8" t="inlineStr">
+      <c r="X28" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -17108,12 +17108,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE28" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF28" s="8" t="inlineStr">
+      <c r="AE28" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF28" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -17128,19 +17128,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI28" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AJ28" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AK28" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AI28" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AJ28" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AK28" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AL28" s="6" t="inlineStr">
@@ -17193,7 +17193,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AV28" s="8" t="inlineStr">
+      <c r="AV28" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -17203,17 +17203,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX28" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AY28" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AZ28" s="8" t="inlineStr">
+      <c r="AX28" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AY28" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AZ28" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -17228,9 +17228,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC28" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BC28" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -17255,9 +17255,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E29" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F29" s="6" t="inlineStr">
@@ -17335,7 +17335,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U29" s="8" t="inlineStr">
+      <c r="U29" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -17350,7 +17350,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="X29" s="8" t="inlineStr">
+      <c r="X29" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -17385,12 +17385,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE29" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF29" s="8" t="inlineStr">
+      <c r="AE29" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF29" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -17405,19 +17405,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI29" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AJ29" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AK29" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AI29" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AJ29" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AK29" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AL29" s="6" t="inlineStr">
@@ -17470,7 +17470,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AV29" s="8" t="inlineStr">
+      <c r="AV29" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -17480,17 +17480,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX29" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AY29" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AZ29" s="8" t="inlineStr">
+      <c r="AX29" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AY29" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AZ29" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -17505,9 +17505,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC29" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BC29" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -17532,9 +17532,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E30" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="E30" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F30" s="6" t="inlineStr">
@@ -17612,7 +17612,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U30" s="8" t="inlineStr">
+      <c r="U30" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -17627,7 +17627,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="X30" s="8" t="inlineStr">
+      <c r="X30" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -17662,12 +17662,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE30" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF30" s="8" t="inlineStr">
+      <c r="AE30" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF30" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -17682,19 +17682,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI30" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AJ30" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AK30" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AI30" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AJ30" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AK30" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AL30" s="6" t="inlineStr">
@@ -17747,7 +17747,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AV30" s="8" t="inlineStr">
+      <c r="AV30" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -17757,17 +17757,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX30" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AY30" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AZ30" s="8" t="inlineStr">
+      <c r="AX30" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AY30" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AZ30" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -17782,9 +17782,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC30" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BC30" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -17809,9 +17809,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E31" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="E31" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F31" s="6" t="inlineStr">
@@ -17889,7 +17889,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U31" s="8" t="inlineStr">
+      <c r="U31" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -17904,7 +17904,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="X31" s="8" t="inlineStr">
+      <c r="X31" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -17939,12 +17939,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE31" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF31" s="8" t="inlineStr">
+      <c r="AE31" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF31" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -17959,19 +17959,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI31" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AJ31" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AK31" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AI31" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AJ31" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AK31" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AL31" s="6" t="inlineStr">
@@ -18024,7 +18024,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AV31" s="8" t="inlineStr">
+      <c r="AV31" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -18034,17 +18034,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX31" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AY31" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AZ31" s="8" t="inlineStr">
+      <c r="AX31" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AY31" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AZ31" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -18059,9 +18059,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC31" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BC31" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -18081,12 +18081,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D32" s="7" t="inlineStr">
+      <c r="D32" s="8" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="E32" s="7" t="inlineStr">
+      <c r="E32" s="8" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
@@ -18141,7 +18141,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="P32" s="8" t="inlineStr">
+      <c r="P32" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -18166,7 +18166,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U32" s="8" t="inlineStr">
+      <c r="U32" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -18181,7 +18181,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="X32" s="8" t="inlineStr">
+      <c r="X32" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -18216,12 +18216,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE32" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF32" s="8" t="inlineStr">
+      <c r="AE32" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF32" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -18236,17 +18236,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI32" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AJ32" s="7" t="inlineStr">
+      <c r="AI32" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AJ32" s="8" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AK32" s="7" t="inlineStr">
+      <c r="AK32" s="8" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
@@ -18301,7 +18301,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AV32" s="8" t="inlineStr">
+      <c r="AV32" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -18311,17 +18311,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX32" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AY32" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AZ32" s="8" t="inlineStr">
+      <c r="AX32" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AY32" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AZ32" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -18358,14 +18358,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D33" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="E33" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E33" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F33" s="6" t="inlineStr">
@@ -18418,7 +18418,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="P33" s="8" t="inlineStr">
+      <c r="P33" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -18443,7 +18443,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U33" s="8" t="inlineStr">
+      <c r="U33" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -18458,7 +18458,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="X33" s="8" t="inlineStr">
+      <c r="X33" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -18493,12 +18493,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE33" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF33" s="8" t="inlineStr">
+      <c r="AE33" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF33" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -18513,19 +18513,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI33" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AJ33" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AK33" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AI33" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AJ33" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AK33" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AL33" s="6" t="inlineStr">
@@ -18578,7 +18578,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AV33" s="8" t="inlineStr">
+      <c r="AV33" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -18588,17 +18588,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX33" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AY33" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AZ33" s="8" t="inlineStr">
+      <c r="AX33" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AY33" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AZ33" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -18613,9 +18613,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC33" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BC33" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -18635,12 +18635,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D34" s="7" t="inlineStr">
+      <c r="D34" s="8" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="E34" s="7" t="inlineStr">
+      <c r="E34" s="8" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
@@ -18695,12 +18695,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="P34" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q34" s="8" t="inlineStr">
+      <c r="P34" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q34" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -18720,7 +18720,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U34" s="8" t="inlineStr">
+      <c r="U34" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -18735,7 +18735,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="X34" s="8" t="inlineStr">
+      <c r="X34" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -18770,12 +18770,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE34" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF34" s="8" t="inlineStr">
+      <c r="AE34" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF34" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -18790,17 +18790,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI34" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AJ34" s="7" t="inlineStr">
+      <c r="AI34" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AJ34" s="8" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AK34" s="7" t="inlineStr">
+      <c r="AK34" s="8" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
@@ -18820,12 +18820,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AO34" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AP34" s="8" t="inlineStr">
+      <c r="AO34" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AP34" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -18855,7 +18855,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AV34" s="8" t="inlineStr">
+      <c r="AV34" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -18865,17 +18865,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX34" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AY34" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AZ34" s="8" t="inlineStr">
+      <c r="AX34" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AY34" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AZ34" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -18912,14 +18912,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D35" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="E35" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E35" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F35" s="6" t="inlineStr">
@@ -18972,12 +18972,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="P35" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q35" s="8" t="inlineStr">
+      <c r="P35" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q35" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -18997,7 +18997,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U35" s="8" t="inlineStr">
+      <c r="U35" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -19012,7 +19012,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="X35" s="8" t="inlineStr">
+      <c r="X35" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -19047,12 +19047,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE35" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF35" s="8" t="inlineStr">
+      <c r="AE35" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF35" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -19067,19 +19067,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI35" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AJ35" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AK35" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AI35" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AJ35" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AK35" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AL35" s="6" t="inlineStr">
@@ -19097,12 +19097,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AO35" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AP35" s="8" t="inlineStr">
+      <c r="AO35" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AP35" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -19132,7 +19132,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AV35" s="8" t="inlineStr">
+      <c r="AV35" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -19142,17 +19142,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX35" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AY35" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AZ35" s="8" t="inlineStr">
+      <c r="AX35" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AY35" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AZ35" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -19167,9 +19167,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC35" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BC35" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -19194,9 +19194,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E36" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="E36" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F36" s="6" t="inlineStr">
@@ -19254,7 +19254,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Q36" s="8" t="inlineStr">
+      <c r="Q36" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -19274,7 +19274,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U36" s="8" t="inlineStr">
+      <c r="U36" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -19289,7 +19289,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="X36" s="8" t="inlineStr">
+      <c r="X36" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -19324,12 +19324,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE36" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF36" s="8" t="inlineStr">
+      <c r="AE36" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF36" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -19344,19 +19344,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI36" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AJ36" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AK36" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AI36" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AJ36" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AK36" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AL36" s="6" t="inlineStr">
@@ -19409,7 +19409,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AV36" s="8" t="inlineStr">
+      <c r="AV36" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -19419,17 +19419,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX36" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AY36" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AZ36" s="8" t="inlineStr">
+      <c r="AX36" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AY36" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AZ36" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -19444,9 +19444,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC36" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BC36" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -19471,9 +19471,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E37" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="E37" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F37" s="6" t="inlineStr">
@@ -19521,7 +19521,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O37" s="8" t="inlineStr">
+      <c r="O37" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -19531,7 +19531,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Q37" s="8" t="inlineStr">
+      <c r="Q37" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -19551,7 +19551,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U37" s="8" t="inlineStr">
+      <c r="U37" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -19566,7 +19566,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="X37" s="8" t="inlineStr">
+      <c r="X37" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -19601,12 +19601,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE37" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF37" s="8" t="inlineStr">
+      <c r="AE37" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF37" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -19621,19 +19621,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI37" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AJ37" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AK37" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AI37" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AJ37" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AK37" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AL37" s="6" t="inlineStr">
@@ -19651,12 +19651,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AO37" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AP37" s="8" t="inlineStr">
+      <c r="AO37" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AP37" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -19686,7 +19686,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AV37" s="8" t="inlineStr">
+      <c r="AV37" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -19696,17 +19696,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX37" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AY37" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AZ37" s="8" t="inlineStr">
+      <c r="AX37" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AY37" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AZ37" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -19721,9 +19721,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC37" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BC37" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -19748,7 +19748,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E38" s="7" t="inlineStr">
+      <c r="E38" s="8" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
@@ -19808,7 +19808,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Q38" s="8" t="inlineStr">
+      <c r="Q38" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -19828,7 +19828,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U38" s="8" t="inlineStr">
+      <c r="U38" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -19843,7 +19843,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="X38" s="8" t="inlineStr">
+      <c r="X38" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -19878,12 +19878,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE38" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF38" s="8" t="inlineStr">
+      <c r="AE38" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF38" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -19898,17 +19898,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI38" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AJ38" s="7" t="inlineStr">
+      <c r="AI38" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AJ38" s="8" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AK38" s="7" t="inlineStr">
+      <c r="AK38" s="8" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
@@ -19928,12 +19928,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AO38" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AP38" s="8" t="inlineStr">
+      <c r="AO38" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AP38" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -19963,7 +19963,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AV38" s="8" t="inlineStr">
+      <c r="AV38" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -19973,17 +19973,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX38" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AY38" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AZ38" s="8" t="inlineStr">
+      <c r="AX38" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AY38" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AZ38" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -20025,7 +20025,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E39" s="7" t="inlineStr">
+      <c r="E39" s="8" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
@@ -20085,7 +20085,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Q39" s="8" t="inlineStr">
+      <c r="Q39" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -20105,7 +20105,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U39" s="8" t="inlineStr">
+      <c r="U39" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -20120,7 +20120,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="X39" s="8" t="inlineStr">
+      <c r="X39" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -20155,12 +20155,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE39" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF39" s="8" t="inlineStr">
+      <c r="AE39" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF39" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -20175,17 +20175,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI39" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AJ39" s="7" t="inlineStr">
+      <c r="AI39" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AJ39" s="8" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AK39" s="7" t="inlineStr">
+      <c r="AK39" s="8" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
@@ -20240,7 +20240,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AV39" s="8" t="inlineStr">
+      <c r="AV39" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -20250,17 +20250,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX39" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AY39" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AZ39" s="8" t="inlineStr">
+      <c r="AX39" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AY39" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AZ39" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -20302,9 +20302,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E40" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="E40" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F40" s="6" t="inlineStr">
@@ -20362,7 +20362,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Q40" s="8" t="inlineStr">
+      <c r="Q40" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -20382,7 +20382,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U40" s="8" t="inlineStr">
+      <c r="U40" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -20397,7 +20397,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="X40" s="8" t="inlineStr">
+      <c r="X40" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -20432,12 +20432,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE40" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF40" s="8" t="inlineStr">
+      <c r="AE40" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF40" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -20452,19 +20452,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI40" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AJ40" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AK40" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AI40" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AJ40" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AK40" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AL40" s="6" t="inlineStr">
@@ -20517,7 +20517,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AV40" s="8" t="inlineStr">
+      <c r="AV40" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -20527,17 +20527,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX40" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AY40" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AZ40" s="8" t="inlineStr">
+      <c r="AX40" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AY40" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AZ40" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -20552,9 +20552,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC40" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BC40" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -20579,9 +20579,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E41" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="E41" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F41" s="6" t="inlineStr">
@@ -20639,7 +20639,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Q41" s="8" t="inlineStr">
+      <c r="Q41" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -20659,7 +20659,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U41" s="8" t="inlineStr">
+      <c r="U41" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -20674,7 +20674,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="X41" s="8" t="inlineStr">
+      <c r="X41" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -20709,12 +20709,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE41" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF41" s="8" t="inlineStr">
+      <c r="AE41" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF41" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -20729,19 +20729,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI41" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AJ41" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AK41" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AI41" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AJ41" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AK41" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AL41" s="6" t="inlineStr">
@@ -20794,7 +20794,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AV41" s="8" t="inlineStr">
+      <c r="AV41" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -20804,17 +20804,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX41" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AY41" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AZ41" s="8" t="inlineStr">
+      <c r="AX41" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AY41" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AZ41" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -20829,9 +20829,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC41" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BC41" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -20856,9 +20856,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E42" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="E42" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F42" s="6" t="inlineStr">
@@ -20916,7 +20916,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Q42" s="8" t="inlineStr">
+      <c r="Q42" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -20936,7 +20936,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U42" s="8" t="inlineStr">
+      <c r="U42" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -20951,7 +20951,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="X42" s="8" t="inlineStr">
+      <c r="X42" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -20986,12 +20986,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE42" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF42" s="8" t="inlineStr">
+      <c r="AE42" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF42" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -21006,19 +21006,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI42" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AJ42" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AK42" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AI42" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AJ42" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AK42" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AL42" s="6" t="inlineStr">
@@ -21071,7 +21071,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AV42" s="8" t="inlineStr">
+      <c r="AV42" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -21081,17 +21081,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX42" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AY42" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AZ42" s="8" t="inlineStr">
+      <c r="AX42" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AY42" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AZ42" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -21106,9 +21106,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC42" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BC42" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -21133,9 +21133,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E43" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="E43" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F43" s="6" t="inlineStr">
@@ -21193,7 +21193,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Q43" s="8" t="inlineStr">
+      <c r="Q43" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -21213,7 +21213,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U43" s="8" t="inlineStr">
+      <c r="U43" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -21228,7 +21228,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="X43" s="8" t="inlineStr">
+      <c r="X43" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -21263,12 +21263,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE43" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF43" s="8" t="inlineStr">
+      <c r="AE43" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF43" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -21283,19 +21283,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI43" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AJ43" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AK43" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AI43" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AJ43" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AK43" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AL43" s="6" t="inlineStr">
@@ -21348,7 +21348,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AV43" s="8" t="inlineStr">
+      <c r="AV43" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -21358,17 +21358,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX43" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AY43" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AZ43" s="8" t="inlineStr">
+      <c r="AX43" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AY43" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AZ43" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -21383,9 +21383,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC43" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BC43" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -21405,14 +21405,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D44" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="E44" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E44" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F44" s="6" t="inlineStr">
@@ -21465,12 +21465,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="P44" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q44" s="8" t="inlineStr">
+      <c r="P44" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q44" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -21490,7 +21490,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U44" s="8" t="inlineStr">
+      <c r="U44" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -21505,7 +21505,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="X44" s="8" t="inlineStr">
+      <c r="X44" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -21540,12 +21540,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE44" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF44" s="8" t="inlineStr">
+      <c r="AE44" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF44" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -21560,19 +21560,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI44" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AJ44" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AK44" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AI44" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AJ44" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AK44" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AL44" s="6" t="inlineStr">
@@ -21625,7 +21625,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AV44" s="8" t="inlineStr">
+      <c r="AV44" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -21635,17 +21635,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX44" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AY44" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AZ44" s="8" t="inlineStr">
+      <c r="AX44" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AY44" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AZ44" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -21660,9 +21660,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC44" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BC44" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -21682,14 +21682,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D45" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="E45" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E45" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F45" s="6" t="inlineStr">
@@ -21742,12 +21742,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="P45" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q45" s="8" t="inlineStr">
+      <c r="P45" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q45" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -21767,7 +21767,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U45" s="8" t="inlineStr">
+      <c r="U45" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -21782,7 +21782,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="X45" s="8" t="inlineStr">
+      <c r="X45" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -21817,12 +21817,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE45" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF45" s="8" t="inlineStr">
+      <c r="AE45" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF45" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -21837,19 +21837,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI45" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AJ45" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AK45" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AI45" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AJ45" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AK45" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AL45" s="6" t="inlineStr">
@@ -21902,7 +21902,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AV45" s="8" t="inlineStr">
+      <c r="AV45" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -21912,17 +21912,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX45" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AY45" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AZ45" s="8" t="inlineStr">
+      <c r="AX45" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AY45" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AZ45" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -21937,9 +21937,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC45" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BC45" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -21959,14 +21959,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D46" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="E46" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="D46" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E46" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F46" s="6" t="inlineStr">
@@ -22019,12 +22019,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="P46" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q46" s="8" t="inlineStr">
+      <c r="P46" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q46" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -22044,7 +22044,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U46" s="8" t="inlineStr">
+      <c r="U46" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -22059,7 +22059,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="X46" s="8" t="inlineStr">
+      <c r="X46" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -22094,12 +22094,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE46" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF46" s="8" t="inlineStr">
+      <c r="AE46" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF46" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -22114,19 +22114,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI46" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AJ46" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AK46" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AI46" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AJ46" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AK46" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AL46" s="6" t="inlineStr">
@@ -22144,12 +22144,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AO46" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AP46" s="8" t="inlineStr">
+      <c r="AO46" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AP46" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -22179,7 +22179,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AV46" s="8" t="inlineStr">
+      <c r="AV46" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -22189,17 +22189,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX46" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AY46" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AZ46" s="8" t="inlineStr">
+      <c r="AX46" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AY46" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AZ46" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -22214,9 +22214,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC46" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BC46" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -22236,14 +22236,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D47" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="E47" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E47" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F47" s="6" t="inlineStr">
@@ -22296,12 +22296,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="P47" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q47" s="8" t="inlineStr">
+      <c r="P47" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q47" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -22321,7 +22321,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U47" s="8" t="inlineStr">
+      <c r="U47" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -22336,7 +22336,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="X47" s="8" t="inlineStr">
+      <c r="X47" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -22371,12 +22371,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE47" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF47" s="8" t="inlineStr">
+      <c r="AE47" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF47" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -22391,19 +22391,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI47" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AJ47" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AK47" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AI47" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AJ47" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AK47" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AL47" s="6" t="inlineStr">
@@ -22421,12 +22421,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AO47" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AP47" s="8" t="inlineStr">
+      <c r="AO47" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AP47" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -22456,7 +22456,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AV47" s="8" t="inlineStr">
+      <c r="AV47" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -22466,17 +22466,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX47" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AY47" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AZ47" s="8" t="inlineStr">
+      <c r="AX47" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AY47" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AZ47" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -22491,9 +22491,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC47" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BC47" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -22518,9 +22518,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E48" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="E48" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F48" s="6" t="inlineStr">
@@ -22598,7 +22598,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U48" s="8" t="inlineStr">
+      <c r="U48" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -22618,12 +22618,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Y48" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z48" s="8" t="inlineStr">
+      <c r="Y48" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z48" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -22648,12 +22648,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE48" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF48" s="8" t="inlineStr">
+      <c r="AE48" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF48" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -22668,19 +22668,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI48" s="8" t="inlineStr">
+      <c r="AI48" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AJ48" s="7" t="inlineStr">
         <is>
-          <t>AMBIGUOUS</t>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AK48" s="7" t="inlineStr">
         <is>
-          <t>AMBIGUOUS</t>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AL48" s="6" t="inlineStr">
@@ -22698,12 +22698,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AO48" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AP48" s="8" t="inlineStr">
+      <c r="AO48" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AP48" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -22733,7 +22733,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AV48" s="8" t="inlineStr">
+      <c r="AV48" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -22743,17 +22743,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX48" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AY48" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AZ48" s="8" t="inlineStr">
+      <c r="AX48" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AY48" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AZ48" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -22768,9 +22768,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC48" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BC48" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -22795,9 +22795,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E49" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="E49" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F49" s="6" t="inlineStr">
@@ -22875,7 +22875,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U49" s="8" t="inlineStr">
+      <c r="U49" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -22895,12 +22895,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Y49" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z49" s="8" t="inlineStr">
+      <c r="Y49" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z49" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -22925,12 +22925,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE49" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF49" s="8" t="inlineStr">
+      <c r="AE49" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF49" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -22945,19 +22945,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI49" s="8" t="inlineStr">
+      <c r="AI49" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AJ49" s="7" t="inlineStr">
         <is>
-          <t>AMBIGUOUS</t>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AK49" s="7" t="inlineStr">
         <is>
-          <t>AMBIGUOUS</t>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AL49" s="6" t="inlineStr">
@@ -23000,7 +23000,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT49" s="8" t="inlineStr">
+      <c r="AT49" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -23010,7 +23010,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AV49" s="8" t="inlineStr">
+      <c r="AV49" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -23020,17 +23020,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX49" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AY49" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AZ49" s="8" t="inlineStr">
+      <c r="AX49" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AY49" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AZ49" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -23045,9 +23045,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC49" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BC49" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -23072,9 +23072,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E50" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="E50" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F50" s="6" t="inlineStr">
@@ -23152,7 +23152,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U50" s="8" t="inlineStr">
+      <c r="U50" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -23172,12 +23172,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Y50" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z50" s="8" t="inlineStr">
+      <c r="Y50" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z50" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -23202,12 +23202,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE50" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF50" s="8" t="inlineStr">
+      <c r="AE50" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF50" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -23222,19 +23222,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI50" s="8" t="inlineStr">
+      <c r="AI50" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AJ50" s="7" t="inlineStr">
         <is>
-          <t>AMBIGUOUS</t>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AK50" s="7" t="inlineStr">
         <is>
-          <t>AMBIGUOUS</t>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AL50" s="6" t="inlineStr">
@@ -23252,12 +23252,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AO50" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AP50" s="8" t="inlineStr">
+      <c r="AO50" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AP50" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -23287,7 +23287,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AV50" s="8" t="inlineStr">
+      <c r="AV50" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -23297,17 +23297,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX50" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AY50" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AZ50" s="8" t="inlineStr">
+      <c r="AX50" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AY50" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AZ50" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -23322,9 +23322,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC50" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BC50" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -23349,9 +23349,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E51" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="E51" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F51" s="6" t="inlineStr">
@@ -23429,7 +23429,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U51" s="8" t="inlineStr">
+      <c r="U51" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -23449,12 +23449,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Y51" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z51" s="8" t="inlineStr">
+      <c r="Y51" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z51" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -23479,12 +23479,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE51" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF51" s="8" t="inlineStr">
+      <c r="AE51" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF51" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -23499,19 +23499,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI51" s="8" t="inlineStr">
+      <c r="AI51" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AJ51" s="7" t="inlineStr">
         <is>
-          <t>AMBIGUOUS</t>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AK51" s="7" t="inlineStr">
         <is>
-          <t>AMBIGUOUS</t>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AL51" s="6" t="inlineStr">
@@ -23564,7 +23564,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AV51" s="8" t="inlineStr">
+      <c r="AV51" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -23574,17 +23574,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX51" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AY51" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AZ51" s="8" t="inlineStr">
+      <c r="AX51" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AY51" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AZ51" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -23599,9 +23599,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC51" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BC51" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -23620,7 +23620,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D133"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -23654,12 +23654,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>STM32MP215D</t>
+          <t>STM32MP251A</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -23669,19 +23669,19 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Table 1. STM32MP21xA/D features and peripheral counts lists VFBGA225 (8x8 pitch 0.5 mm), VFBGA273 (11x11 pitch 0.5 mm) for this family; the table gives no key to tie a package to this part</t>
+          <t>cover names Arm Cortex-A35, Arm Cortex-M33, Arm Cortex-M0+; ST reports the application core here and the others as co-processors</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>STM32MP215D</t>
+          <t>STM32MP251A</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -23691,19 +23691,19 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>cover names Arm Cortex-A35, Arm Cortex-M33; ST reports the application core here and the others as co-processors</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>STM32MP215D</t>
+          <t>STM32MP251A</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -23720,12 +23720,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>STM32MP215D</t>
+          <t>STM32MP251C</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -23735,19 +23735,19 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>cover names Arm Cortex-A35, Arm Cortex-M33, Arm Cortex-M0+; ST reports the application core here and the others as co-processors</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>STM32MP215F</t>
+          <t>STM32MP251C</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -23757,19 +23757,19 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Table 1. STM32MP21xC/F features and peripheral counts lists TFBGA289 (14x14 pitch 0.8 mm), VFBGA225 (8x8 pitch 0.5 mm), VFBGA273 (11x11 pitch 0.5 mm), VFBGA361 (10x10 pitch 0.5 mm) for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>STM32MP215F</t>
+          <t>STM32MP251C</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -23779,19 +23779,19 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>cover names Arm Cortex-A35, Arm Cortex-M33; ST reports the application core here and the others as co-processors</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>STM32MP215F</t>
+          <t>STM32MP211C</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -23801,19 +23801,19 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 0), and the table does not say which timers the variant omits</t>
+          <t>Table 1. STM32MP21xC/F features and peripheral counts lists TFBGA289 (14x14 pitch 0.8 mm), VFBGA225 (8x8 pitch 0.5 mm), VFBGA273 (11x11 pitch 0.5 mm), VFBGA361 (10x10 pitch 0.5 mm) for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>STM32MP215F</t>
+          <t>STM32MP211C</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -23823,19 +23823,19 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 0), and the table does not say which timers the variant omits</t>
+          <t>cover names Arm Cortex-A35, Arm Cortex-M33; ST reports the application core here and the others as co-processors</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>STM32MP215A</t>
+          <t>STM32MP211C</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -23845,19 +23845,19 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Table 1. STM32MP21xA/D features and peripheral counts lists VFBGA225 (8x8 pitch 0.5 mm), VFBGA273 (11x11 pitch 0.5 mm) for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 0), and the table does not say which timers the variant omits</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>STM32MP215A</t>
+          <t>STM32MP211C</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -23867,19 +23867,19 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>cover names Arm Cortex-A35, Arm Cortex-M33; ST reports the application core here and the others as co-processors</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 0), and the table does not say which timers the variant omits</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>STM32MP215A</t>
+          <t>STM32MP211A</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -23889,19 +23889,19 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 1. STM32MP21xA/D features and peripheral counts lists VFBGA225 (8x8 pitch 0.5 mm), VFBGA273 (11x11 pitch 0.5 mm) for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>STM32MP215A</t>
+          <t>STM32MP211A</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -23911,19 +23911,19 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>cover names Arm Cortex-A35, Arm Cortex-M33; ST reports the application core here and the others as co-processors</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>STM32MP215C</t>
+          <t>STM32MP211A</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -23933,19 +23933,19 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Table 1. STM32MP21xC/F features and peripheral counts lists TFBGA289 (14x14 pitch 0.8 mm), VFBGA225 (8x8 pitch 0.5 mm), VFBGA273 (11x11 pitch 0.5 mm), VFBGA361 (10x10 pitch 0.5 mm) for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>STM32MP215C</t>
+          <t>STM32MP211A</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -23955,19 +23955,19 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>cover names Arm Cortex-A35, Arm Cortex-M33; ST reports the application core here and the others as co-processors</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>STM32MP215C</t>
+          <t>STM32MP231A</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -23977,19 +23977,19 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 0), and the table does not say which timers the variant omits</t>
+          <t>cover names Arm Cortex-A35, Arm Cortex-M33; ST reports the application core here and the others as co-processors</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>STM32MP215C</t>
+          <t>STM32MP231A</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -23999,19 +23999,19 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 0), and the table does not say which timers the variant omits</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>STM32MP255F</t>
+          <t>STM32MP231A</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -24021,19 +24021,19 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>cover names Arm Cortex-A35, Arm Cortex-M33, Arm Cortex-M0+; ST reports the application core here and the others as co-processors</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>STM32MP255F</t>
+          <t>STM32MP231C</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -24043,19 +24043,19 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>cover names Arm Cortex-A35, Arm Cortex-M33; ST reports the application core here and the others as co-processors</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>STM32MP255F</t>
+          <t>STM32MP231C</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -24072,12 +24072,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>STM32MP255A</t>
+          <t>STM32MP231C</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -24086,2470 +24086,6 @@
         </is>
       </c>
       <c r="D21" t="inlineStr">
-        <is>
-          <t>cover names Arm Cortex-A35, Arm Cortex-M33, Arm Cortex-M0+; ST reports the application core here and the others as co-processors</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>STM32MP255A</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>STM32MP255A</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>STM32MP255C</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>cover names Arm Cortex-A35, Arm Cortex-M33, Arm Cortex-M0+; ST reports the application core here and the others as co-processors</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>STM32MP255C</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>STM32MP255C</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>STM32MP255D</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>cover names Arm Cortex-A35, Arm Cortex-M33, Arm Cortex-M0+; ST reports the application core here and the others as co-processors</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>STM32MP255D</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>STM32MP255D</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>STM32MP251A</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>cover names Arm Cortex-A35, Arm Cortex-M33, Arm Cortex-M0+; ST reports the application core here and the others as co-processors</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>STM32MP251A</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>STM32MP251A</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>STM32MP251C</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>cover names Arm Cortex-A35, Arm Cortex-M33, Arm Cortex-M0+; ST reports the application core here and the others as co-processors</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>STM32MP251C</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>STM32MP251C</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>STM32MP251D</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>cover names Arm Cortex-A35, Arm Cortex-M33, Arm Cortex-M0+; ST reports the application core here and the others as co-processors</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>STM32MP251D</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>STM32MP251D</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>STM32MP251F</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>cover names Arm Cortex-A35, Arm Cortex-M33, Arm Cortex-M0+; ST reports the application core here and the others as co-processors</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>STM32MP251F</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>STM32MP251F</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>STM32MP253F</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>cover names Arm Cortex-A35, Arm Cortex-M33, Arm Cortex-M0+; ST reports the application core here and the others as co-processors</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>STM32MP253F</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>STM32MP253F</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>STM32MP253A</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>cover names Arm Cortex-A35, Arm Cortex-M33, Arm Cortex-M0+; ST reports the application core here and the others as co-processors</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>STM32MP253A</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>STM32MP253A</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>STM32MP253C</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>cover names Arm Cortex-A35, Arm Cortex-M33, Arm Cortex-M0+; ST reports the application core here and the others as co-processors</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>STM32MP253C</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>STM32MP253C</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>STM32MP253D</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>cover names Arm Cortex-A35, Arm Cortex-M33, Arm Cortex-M0+; ST reports the application core here and the others as co-processors</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>STM32MP253D</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>STM32MP253D</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>STM32MP235C</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>cover names Arm Cortex-A35, Arm Cortex-M33; ST reports the application core here and the others as co-processors</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>STM32MP235C</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>STM32MP235C</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>STM32MP235A</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>cover names Arm Cortex-A35, Arm Cortex-M33; ST reports the application core here and the others as co-processors</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>STM32MP235A</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>STM32MP235A</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>STM32MP235D</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>cover names Arm Cortex-A35, Arm Cortex-M33; ST reports the application core here and the others as co-processors</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>STM32MP235D</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>STM32MP235D</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>STM32MP235F</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>cover names Arm Cortex-A35, Arm Cortex-M33; ST reports the application core here and the others as co-processors</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>STM32MP235F</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>STM32MP235F</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>STM32MP211C</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>Table 1. STM32MP21xC/F features and peripheral counts lists TFBGA289 (14x14 pitch 0.8 mm), VFBGA225 (8x8 pitch 0.5 mm), VFBGA273 (11x11 pitch 0.5 mm), VFBGA361 (10x10 pitch 0.5 mm) for this family; the table gives no key to tie a package to this part</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>STM32MP211C</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>cover names Arm Cortex-A35, Arm Cortex-M33; ST reports the application core here and the others as co-processors</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>STM32MP211C</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 0), and the table does not say which timers the variant omits</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>STM32MP211C</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 0), and the table does not say which timers the variant omits</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>STM32MP211F</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>Table 1. STM32MP21xC/F features and peripheral counts lists TFBGA289 (14x14 pitch 0.8 mm), VFBGA225 (8x8 pitch 0.5 mm), VFBGA273 (11x11 pitch 0.5 mm), VFBGA361 (10x10 pitch 0.5 mm) for this family; the table gives no key to tie a package to this part</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>STM32MP211F</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>cover names Arm Cortex-A35, Arm Cortex-M33; ST reports the application core here and the others as co-processors</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>STM32MP211F</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 0), and the table does not say which timers the variant omits</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>STM32MP211F</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 0), and the table does not say which timers the variant omits</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>STM32MP211A</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>Table 1. STM32MP21xA/D features and peripheral counts lists VFBGA225 (8x8 pitch 0.5 mm), VFBGA273 (11x11 pitch 0.5 mm) for this family; the table gives no key to tie a package to this part</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>STM32MP211A</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>cover names Arm Cortex-A35, Arm Cortex-M33; ST reports the application core here and the others as co-processors</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>STM32MP211A</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>STM32MP211A</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>STM32MP211D</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>Table 1. STM32MP21xA/D features and peripheral counts lists VFBGA225 (8x8 pitch 0.5 mm), VFBGA273 (11x11 pitch 0.5 mm) for this family; the table gives no key to tie a package to this part</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>STM32MP211D</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>cover names Arm Cortex-A35, Arm Cortex-M33; ST reports the application core here and the others as co-processors</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>STM32MP211D</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>STM32MP211D</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>STM32MP231F</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>cover names Arm Cortex-A35, Arm Cortex-M33; ST reports the application core here and the others as co-processors</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>STM32MP231F</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>STM32MP231F</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>STM32MP231D</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>cover names Arm Cortex-A35, Arm Cortex-M33; ST reports the application core here and the others as co-processors</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>STM32MP231D</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>STM32MP231D</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>STM32MP231A</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>cover names Arm Cortex-A35, Arm Cortex-M33; ST reports the application core here and the others as co-processors</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>STM32MP231A</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>STM32MP231A</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>STM32MP231C</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>cover names Arm Cortex-A35, Arm Cortex-M33; ST reports the application core here and the others as co-processors</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>STM32MP231C</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>STM32MP231C</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>STM32MP233C</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>cover names Arm Cortex-A35, Arm Cortex-M33; ST reports the application core here and the others as co-processors</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>STM32MP233C</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>STM32MP233C</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>STM32MP233F</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>cover names Arm Cortex-A35, Arm Cortex-M33; ST reports the application core here and the others as co-processors</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>STM32MP233F</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>STM32MP233F</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>STM32MP233A</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>cover names Arm Cortex-A35, Arm Cortex-M33; ST reports the application core here and the others as co-processors</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>STM32MP233A</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>STM32MP233A</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>STM32MP233D</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>cover names Arm Cortex-A35, Arm Cortex-M33; ST reports the application core here and the others as co-processors</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>STM32MP233D</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>STM32MP233D</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>STM32MP213C</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>Table 1. STM32MP21xC/F features and peripheral counts lists TFBGA289 (14x14 pitch 0.8 mm), VFBGA225 (8x8 pitch 0.5 mm), VFBGA273 (11x11 pitch 0.5 mm), VFBGA361 (10x10 pitch 0.5 mm) for this family; the table gives no key to tie a package to this part</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>STM32MP213C</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>cover names Arm Cortex-A35, Arm Cortex-M33; ST reports the application core here and the others as co-processors</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>STM32MP213C</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 0), and the table does not say which timers the variant omits</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>STM32MP213C</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 0), and the table does not say which timers the variant omits</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>STM32MP213F</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>Table 1. STM32MP21xC/F features and peripheral counts lists TFBGA289 (14x14 pitch 0.8 mm), VFBGA225 (8x8 pitch 0.5 mm), VFBGA273 (11x11 pitch 0.5 mm), VFBGA361 (10x10 pitch 0.5 mm) for this family; the table gives no key to tie a package to this part</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>STM32MP213F</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>cover names Arm Cortex-A35, Arm Cortex-M33; ST reports the application core here and the others as co-processors</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>STM32MP213F</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 0), and the table does not say which timers the variant omits</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>STM32MP213F</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 0), and the table does not say which timers the variant omits</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>STM32MP213A</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>Table 1. STM32MP21xA/D features and peripheral counts lists VFBGA225 (8x8 pitch 0.5 mm), VFBGA273 (11x11 pitch 0.5 mm) for this family; the table gives no key to tie a package to this part</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>STM32MP213A</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>cover names Arm Cortex-A35, Arm Cortex-M33; ST reports the application core here and the others as co-processors</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>STM32MP213A</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>STM32MP213A</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>STM32MP213D</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>Table 1. STM32MP21xA/D features and peripheral counts lists VFBGA225 (8x8 pitch 0.5 mm), VFBGA273 (11x11 pitch 0.5 mm) for this family; the table gives no key to tie a package to this part</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>STM32MP213D</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>cover names Arm Cortex-A35, Arm Cortex-M33; ST reports the application core here and the others as co-processors</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>STM32MP213D</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>STM32MP213D</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>STM32MP257A</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>cover names Arm Cortex-A35, Arm Cortex-M33, Arm Cortex-M0+; ST reports the application core here and the others as co-processors</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>STM32MP257A</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>STM32MP257A</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>STM32MP257C</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>cover names Arm Cortex-A35, Arm Cortex-M33, Arm Cortex-M0+; ST reports the application core here and the others as co-processors</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>STM32MP257C</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>STM32MP257C</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>STM32MP257D</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>cover names Arm Cortex-A35, Arm Cortex-M33, Arm Cortex-M0+; ST reports the application core here and the others as co-processors</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>STM32MP257D</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>STM32MP257D</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>STM32MP257F</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>cover names Arm Cortex-A35, Arm Cortex-M33, Arm Cortex-M0+; ST reports the application core here and the others as co-processors</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>STM32MP257F</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>STM32MP257F</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
         <is>
           <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>

--- a/product_selector_out/STM32MP2 series.xlsx
+++ b/product_selector_out/STM32MP2 series.xlsx
@@ -61,12 +61,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
+        <fgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFEB9C"/>
+        <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
   </fills>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="BC12" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32mp211a.pdf</t>
         </is>
       </c>
     </row>
@@ -1461,7 +1461,7 @@
       </c>
       <c r="BC13" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32mp211c.pdf</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="BC14" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32mp211a.pdf</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="BC15" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32mp211c.pdf</t>
         </is>
       </c>
     </row>
@@ -2292,7 +2292,7 @@
       </c>
       <c r="BC16" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32mp251c.pdf</t>
         </is>
       </c>
     </row>
@@ -2569,7 +2569,7 @@
       </c>
       <c r="BC17" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32mp251a.pdf</t>
         </is>
       </c>
     </row>
@@ -2846,7 +2846,7 @@
       </c>
       <c r="BC18" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32mp251c.pdf</t>
         </is>
       </c>
     </row>
@@ -3123,7 +3123,7 @@
       </c>
       <c r="BC19" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32mp251a.pdf</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="BC22" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32mp251a.pdf</t>
         </is>
       </c>
     </row>
@@ -4231,7 +4231,7 @@
       </c>
       <c r="BC23" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32mp251c.pdf</t>
         </is>
       </c>
     </row>
@@ -4508,7 +4508,7 @@
       </c>
       <c r="BC24" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32mp251c.pdf</t>
         </is>
       </c>
     </row>
@@ -4785,7 +4785,7 @@
       </c>
       <c r="BC25" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32mp251a.pdf</t>
         </is>
       </c>
     </row>
@@ -5062,7 +5062,7 @@
       </c>
       <c r="BC26" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32mp251c.pdf</t>
         </is>
       </c>
     </row>
@@ -5339,7 +5339,7 @@
       </c>
       <c r="BC27" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32mp251a.pdf</t>
         </is>
       </c>
     </row>
@@ -5616,7 +5616,7 @@
       </c>
       <c r="BC28" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32mp231c.pdf</t>
         </is>
       </c>
     </row>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="BC29" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32mp231a.pdf</t>
         </is>
       </c>
     </row>
@@ -6170,7 +6170,7 @@
       </c>
       <c r="BC30" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32mp231a.pdf</t>
         </is>
       </c>
     </row>
@@ -6447,7 +6447,7 @@
       </c>
       <c r="BC31" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32mp231c.pdf</t>
         </is>
       </c>
     </row>
@@ -7001,7 +7001,7 @@
       </c>
       <c r="BC33" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32mp211c.pdf</t>
         </is>
       </c>
     </row>
@@ -7555,7 +7555,7 @@
       </c>
       <c r="BC35" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32mp211a.pdf</t>
         </is>
       </c>
     </row>
@@ -7832,7 +7832,7 @@
       </c>
       <c r="BC36" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32mp231c.pdf</t>
         </is>
       </c>
     </row>
@@ -8109,7 +8109,7 @@
       </c>
       <c r="BC37" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32mp231a.pdf</t>
         </is>
       </c>
     </row>
@@ -8940,7 +8940,7 @@
       </c>
       <c r="BC40" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32mp231c.pdf</t>
         </is>
       </c>
     </row>
@@ -9217,7 +9217,7 @@
       </c>
       <c r="BC41" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32mp231c.pdf</t>
         </is>
       </c>
     </row>
@@ -9494,7 +9494,7 @@
       </c>
       <c r="BC42" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32mp231a.pdf</t>
         </is>
       </c>
     </row>
@@ -9771,7 +9771,7 @@
       </c>
       <c r="BC43" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32mp231a.pdf</t>
         </is>
       </c>
     </row>
@@ -10048,7 +10048,7 @@
       </c>
       <c r="BC44" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32mp211c.pdf</t>
         </is>
       </c>
     </row>
@@ -10325,7 +10325,7 @@
       </c>
       <c r="BC45" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32mp211c.pdf</t>
         </is>
       </c>
     </row>
@@ -10602,7 +10602,7 @@
       </c>
       <c r="BC46" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32mp211a.pdf</t>
         </is>
       </c>
     </row>
@@ -10879,7 +10879,7 @@
       </c>
       <c r="BC47" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32mp211a.pdf</t>
         </is>
       </c>
     </row>
@@ -11156,7 +11156,7 @@
       </c>
       <c r="BC48" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32mp251a.pdf</t>
         </is>
       </c>
     </row>
@@ -11433,7 +11433,7 @@
       </c>
       <c r="BC49" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32mp251c.pdf</t>
         </is>
       </c>
     </row>
@@ -11710,7 +11710,7 @@
       </c>
       <c r="BC50" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32mp251a.pdf</t>
         </is>
       </c>
     </row>
@@ -11987,7 +11987,7 @@
       </c>
       <c r="BC51" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32mp251c.pdf</t>
         </is>
       </c>
     </row>
@@ -12541,14 +12541,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="E12" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="F12" s="6" t="inlineStr">
@@ -12606,7 +12606,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Q12" s="7" t="inlineStr">
+      <c r="Q12" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12626,7 +12626,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U12" s="7" t="inlineStr">
+      <c r="U12" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12641,7 +12641,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="X12" s="7" t="inlineStr">
+      <c r="X12" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12676,12 +12676,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF12" s="7" t="inlineStr">
+      <c r="AE12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF12" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12696,19 +12696,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AJ12" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AK12" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AI12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AJ12" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AK12" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AL12" s="6" t="inlineStr">
@@ -12726,12 +12726,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AO12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AP12" s="7" t="inlineStr">
+      <c r="AO12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AP12" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12761,7 +12761,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AV12" s="7" t="inlineStr">
+      <c r="AV12" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12771,34 +12771,34 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AY12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AZ12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BA12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BB12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BC12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="AX12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AY12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AZ12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BA12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BB12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BC12" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -12818,14 +12818,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="E13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
@@ -12883,7 +12883,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Q13" s="7" t="inlineStr">
+      <c r="Q13" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12903,7 +12903,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U13" s="7" t="inlineStr">
+      <c r="U13" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12918,7 +12918,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="X13" s="7" t="inlineStr">
+      <c r="X13" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12953,12 +12953,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF13" s="7" t="inlineStr">
+      <c r="AE13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF13" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12973,19 +12973,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AJ13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AK13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AI13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AJ13" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AK13" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AL13" s="6" t="inlineStr">
@@ -13038,7 +13038,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AV13" s="7" t="inlineStr">
+      <c r="AV13" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13048,17 +13048,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AY13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AZ13" s="7" t="inlineStr">
+      <c r="AX13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AY13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AZ13" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13073,9 +13073,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BC13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -13095,14 +13095,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="E14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
@@ -13160,7 +13160,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Q14" s="7" t="inlineStr">
+      <c r="Q14" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13180,7 +13180,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U14" s="7" t="inlineStr">
+      <c r="U14" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13195,7 +13195,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="X14" s="7" t="inlineStr">
+      <c r="X14" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13230,12 +13230,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF14" s="7" t="inlineStr">
+      <c r="AE14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF14" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13250,19 +13250,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AJ14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AK14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AI14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AJ14" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AK14" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AL14" s="6" t="inlineStr">
@@ -13280,12 +13280,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AO14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AP14" s="7" t="inlineStr">
+      <c r="AO14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AP14" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13315,7 +13315,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AV14" s="7" t="inlineStr">
+      <c r="AV14" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13325,17 +13325,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AY14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AZ14" s="7" t="inlineStr">
+      <c r="AX14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AY14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AZ14" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13350,9 +13350,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BC14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -13372,14 +13372,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="E15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
@@ -13437,7 +13437,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Q15" s="7" t="inlineStr">
+      <c r="Q15" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13457,7 +13457,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U15" s="7" t="inlineStr">
+      <c r="U15" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13472,7 +13472,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="X15" s="7" t="inlineStr">
+      <c r="X15" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13507,12 +13507,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF15" s="7" t="inlineStr">
+      <c r="AE15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF15" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13527,19 +13527,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AJ15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AK15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AI15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AJ15" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AK15" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AL15" s="6" t="inlineStr">
@@ -13592,7 +13592,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AV15" s="7" t="inlineStr">
+      <c r="AV15" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13602,17 +13602,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AY15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AZ15" s="7" t="inlineStr">
+      <c r="AX15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AY15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AZ15" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13627,9 +13627,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BC15" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -13654,9 +13654,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr">
@@ -13734,7 +13734,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U16" s="7" t="inlineStr">
+      <c r="U16" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13754,12 +13754,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Y16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z16" s="7" t="inlineStr">
+      <c r="Y16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z16" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13784,12 +13784,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF16" s="7" t="inlineStr">
+      <c r="AE16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF16" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13804,19 +13804,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI16" s="7" t="inlineStr">
+      <c r="AI16" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AJ16" s="7" t="inlineStr">
         <is>
-          <t>UNAVAILABLE</t>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AK16" s="7" t="inlineStr">
         <is>
-          <t>UNAVAILABLE</t>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AL16" s="6" t="inlineStr">
@@ -13869,7 +13869,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AV16" s="7" t="inlineStr">
+      <c r="AV16" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13879,17 +13879,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AY16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AZ16" s="7" t="inlineStr">
+      <c r="AX16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AY16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AZ16" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -13904,9 +13904,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BC16" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -13931,9 +13931,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E17" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
@@ -14011,7 +14011,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U17" s="7" t="inlineStr">
+      <c r="U17" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -14031,12 +14031,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Y17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z17" s="7" t="inlineStr">
+      <c r="Y17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z17" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -14061,12 +14061,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF17" s="7" t="inlineStr">
+      <c r="AE17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF17" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -14081,19 +14081,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI17" s="7" t="inlineStr">
+      <c r="AI17" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AJ17" s="7" t="inlineStr">
         <is>
-          <t>UNAVAILABLE</t>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AK17" s="7" t="inlineStr">
         <is>
-          <t>UNAVAILABLE</t>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AL17" s="6" t="inlineStr">
@@ -14111,12 +14111,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AO17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AP17" s="7" t="inlineStr">
+      <c r="AO17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AP17" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -14146,7 +14146,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AV17" s="7" t="inlineStr">
+      <c r="AV17" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -14156,17 +14156,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AY17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AZ17" s="7" t="inlineStr">
+      <c r="AX17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AY17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AZ17" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -14181,9 +14181,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BC17" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -14208,9 +14208,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E18" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="F18" s="6" t="inlineStr">
@@ -14288,7 +14288,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U18" s="7" t="inlineStr">
+      <c r="U18" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -14308,12 +14308,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Y18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z18" s="7" t="inlineStr">
+      <c r="Y18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z18" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -14338,12 +14338,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF18" s="7" t="inlineStr">
+      <c r="AE18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF18" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -14358,19 +14358,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI18" s="7" t="inlineStr">
+      <c r="AI18" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AJ18" s="7" t="inlineStr">
         <is>
-          <t>UNAVAILABLE</t>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AK18" s="7" t="inlineStr">
         <is>
-          <t>UNAVAILABLE</t>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AL18" s="6" t="inlineStr">
@@ -14423,7 +14423,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AV18" s="7" t="inlineStr">
+      <c r="AV18" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -14433,17 +14433,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AY18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AZ18" s="7" t="inlineStr">
+      <c r="AX18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AY18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AZ18" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -14458,9 +14458,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BC18" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -14485,9 +14485,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E19" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
@@ -14565,7 +14565,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U19" s="7" t="inlineStr">
+      <c r="U19" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -14585,12 +14585,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Y19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z19" s="7" t="inlineStr">
+      <c r="Y19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z19" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -14615,12 +14615,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF19" s="7" t="inlineStr">
+      <c r="AE19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF19" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -14635,19 +14635,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI19" s="7" t="inlineStr">
+      <c r="AI19" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AJ19" s="7" t="inlineStr">
         <is>
-          <t>UNAVAILABLE</t>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AK19" s="7" t="inlineStr">
         <is>
-          <t>UNAVAILABLE</t>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AL19" s="6" t="inlineStr">
@@ -14665,12 +14665,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AO19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AP19" s="7" t="inlineStr">
+      <c r="AO19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AP19" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -14700,7 +14700,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AV19" s="7" t="inlineStr">
+      <c r="AV19" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -14710,17 +14710,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AY19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AZ19" s="7" t="inlineStr">
+      <c r="AX19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AY19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AZ19" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -14735,9 +14735,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BC19" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -14762,7 +14762,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E20" s="8" t="inlineStr">
+      <c r="E20" s="7" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
@@ -14822,7 +14822,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Q20" s="7" t="inlineStr">
+      <c r="Q20" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -14842,12 +14842,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="V20" s="7" t="inlineStr">
+      <c r="U20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="V20" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -14862,12 +14862,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Y20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z20" s="7" t="inlineStr">
+      <c r="Y20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z20" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -14892,12 +14892,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF20" s="7" t="inlineStr">
+      <c r="AE20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF20" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -14912,17 +14912,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AJ20" s="8" t="inlineStr">
+      <c r="AI20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AJ20" s="7" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AK20" s="8" t="inlineStr">
+      <c r="AK20" s="7" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
@@ -14942,12 +14942,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AO20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AP20" s="7" t="inlineStr">
+      <c r="AO20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AP20" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -14977,7 +14977,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AV20" s="7" t="inlineStr">
+      <c r="AV20" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -14987,17 +14987,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AY20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AZ20" s="7" t="inlineStr">
+      <c r="AX20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AY20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AZ20" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -15039,7 +15039,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E21" s="8" t="inlineStr">
+      <c r="E21" s="7" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
@@ -15099,7 +15099,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Q21" s="7" t="inlineStr">
+      <c r="Q21" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -15119,12 +15119,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U21" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="V21" s="7" t="inlineStr">
+      <c r="U21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="V21" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -15139,12 +15139,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Y21" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z21" s="7" t="inlineStr">
+      <c r="Y21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z21" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -15169,12 +15169,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE21" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF21" s="7" t="inlineStr">
+      <c r="AE21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF21" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -15189,17 +15189,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI21" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AJ21" s="8" t="inlineStr">
+      <c r="AI21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AJ21" s="7" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AK21" s="8" t="inlineStr">
+      <c r="AK21" s="7" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
@@ -15254,7 +15254,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AV21" s="7" t="inlineStr">
+      <c r="AV21" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -15264,17 +15264,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX21" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AY21" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AZ21" s="7" t="inlineStr">
+      <c r="AX21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AY21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AZ21" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -15316,9 +15316,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E22" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr">
@@ -15376,7 +15376,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Q22" s="7" t="inlineStr">
+      <c r="Q22" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -15396,12 +15396,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U22" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="V22" s="7" t="inlineStr">
+      <c r="U22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="V22" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -15416,12 +15416,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Y22" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z22" s="7" t="inlineStr">
+      <c r="Y22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z22" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -15446,12 +15446,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE22" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF22" s="7" t="inlineStr">
+      <c r="AE22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF22" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -15466,19 +15466,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI22" s="7" t="inlineStr">
+      <c r="AI22" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AJ22" s="7" t="inlineStr">
         <is>
-          <t>UNAVAILABLE</t>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AK22" s="7" t="inlineStr">
         <is>
-          <t>UNAVAILABLE</t>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AL22" s="6" t="inlineStr">
@@ -15496,12 +15496,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AO22" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AP22" s="7" t="inlineStr">
+      <c r="AO22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AP22" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -15531,7 +15531,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AV22" s="7" t="inlineStr">
+      <c r="AV22" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -15541,17 +15541,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX22" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AY22" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AZ22" s="7" t="inlineStr">
+      <c r="AX22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AY22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AZ22" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -15566,9 +15566,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC22" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BC22" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -15593,9 +15593,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
@@ -15653,7 +15653,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Q23" s="7" t="inlineStr">
+      <c r="Q23" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -15673,12 +15673,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U23" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="V23" s="7" t="inlineStr">
+      <c r="U23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="V23" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -15693,12 +15693,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Y23" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z23" s="7" t="inlineStr">
+      <c r="Y23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z23" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -15723,12 +15723,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE23" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF23" s="7" t="inlineStr">
+      <c r="AE23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF23" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -15743,19 +15743,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI23" s="7" t="inlineStr">
+      <c r="AI23" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AJ23" s="7" t="inlineStr">
         <is>
-          <t>UNAVAILABLE</t>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AK23" s="7" t="inlineStr">
         <is>
-          <t>UNAVAILABLE</t>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AL23" s="6" t="inlineStr">
@@ -15808,7 +15808,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AV23" s="7" t="inlineStr">
+      <c r="AV23" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -15818,17 +15818,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX23" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AY23" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AZ23" s="7" t="inlineStr">
+      <c r="AX23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AY23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AZ23" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -15843,9 +15843,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC23" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BC23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -15870,9 +15870,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E24" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="F24" s="6" t="inlineStr">
@@ -15930,7 +15930,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Q24" s="7" t="inlineStr">
+      <c r="Q24" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -15950,7 +15950,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U24" s="7" t="inlineStr">
+      <c r="U24" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -15960,7 +15960,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W24" s="7" t="inlineStr">
+      <c r="W24" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -15975,7 +15975,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Z24" s="7" t="inlineStr">
+      <c r="Z24" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -16000,12 +16000,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE24" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF24" s="7" t="inlineStr">
+      <c r="AE24" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF24" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -16020,19 +16020,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI24" s="7" t="inlineStr">
+      <c r="AI24" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AJ24" s="7" t="inlineStr">
         <is>
-          <t>UNAVAILABLE</t>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AK24" s="7" t="inlineStr">
         <is>
-          <t>UNAVAILABLE</t>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AL24" s="6" t="inlineStr">
@@ -16085,7 +16085,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AV24" s="7" t="inlineStr">
+      <c r="AV24" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -16095,17 +16095,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX24" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AY24" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AZ24" s="7" t="inlineStr">
+      <c r="AX24" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AY24" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AZ24" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -16120,9 +16120,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC24" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BC24" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -16147,9 +16147,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E25" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="F25" s="6" t="inlineStr">
@@ -16207,7 +16207,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Q25" s="7" t="inlineStr">
+      <c r="Q25" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -16227,7 +16227,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U25" s="7" t="inlineStr">
+      <c r="U25" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -16247,12 +16247,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Y25" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z25" s="7" t="inlineStr">
+      <c r="Y25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z25" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -16277,12 +16277,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE25" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF25" s="7" t="inlineStr">
+      <c r="AE25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF25" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -16297,19 +16297,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI25" s="7" t="inlineStr">
+      <c r="AI25" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AJ25" s="7" t="inlineStr">
         <is>
-          <t>UNAVAILABLE</t>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AK25" s="7" t="inlineStr">
         <is>
-          <t>UNAVAILABLE</t>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AL25" s="6" t="inlineStr">
@@ -16327,12 +16327,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AO25" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AP25" s="7" t="inlineStr">
+      <c r="AO25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AP25" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -16362,7 +16362,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AV25" s="7" t="inlineStr">
+      <c r="AV25" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -16372,17 +16372,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX25" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AY25" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AZ25" s="7" t="inlineStr">
+      <c r="AX25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AY25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AZ25" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -16397,9 +16397,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC25" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BC25" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -16424,9 +16424,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E26" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="F26" s="6" t="inlineStr">
@@ -16484,7 +16484,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Q26" s="7" t="inlineStr">
+      <c r="Q26" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -16504,7 +16504,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U26" s="7" t="inlineStr">
+      <c r="U26" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -16524,12 +16524,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Y26" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z26" s="7" t="inlineStr">
+      <c r="Y26" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z26" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -16554,12 +16554,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE26" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF26" s="7" t="inlineStr">
+      <c r="AE26" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF26" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -16574,19 +16574,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI26" s="7" t="inlineStr">
+      <c r="AI26" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AJ26" s="7" t="inlineStr">
         <is>
-          <t>UNAVAILABLE</t>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AK26" s="7" t="inlineStr">
         <is>
-          <t>UNAVAILABLE</t>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AL26" s="6" t="inlineStr">
@@ -16639,7 +16639,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AV26" s="7" t="inlineStr">
+      <c r="AV26" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -16649,17 +16649,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX26" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AY26" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AZ26" s="7" t="inlineStr">
+      <c r="AX26" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AY26" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AZ26" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -16674,9 +16674,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC26" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BC26" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -16701,9 +16701,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E27" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="F27" s="6" t="inlineStr">
@@ -16761,7 +16761,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Q27" s="7" t="inlineStr">
+      <c r="Q27" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -16781,7 +16781,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U27" s="7" t="inlineStr">
+      <c r="U27" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -16801,12 +16801,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Y27" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z27" s="7" t="inlineStr">
+      <c r="Y27" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z27" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -16831,12 +16831,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE27" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF27" s="7" t="inlineStr">
+      <c r="AE27" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF27" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -16851,19 +16851,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI27" s="7" t="inlineStr">
+      <c r="AI27" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AJ27" s="7" t="inlineStr">
         <is>
-          <t>UNAVAILABLE</t>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AK27" s="7" t="inlineStr">
         <is>
-          <t>UNAVAILABLE</t>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AL27" s="6" t="inlineStr">
@@ -16881,12 +16881,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AO27" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AP27" s="7" t="inlineStr">
+      <c r="AO27" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AP27" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -16916,7 +16916,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AV27" s="7" t="inlineStr">
+      <c r="AV27" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -16926,17 +16926,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX27" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AY27" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AZ27" s="7" t="inlineStr">
+      <c r="AX27" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AY27" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AZ27" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -16951,9 +16951,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC27" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BC27" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -16978,9 +16978,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E28" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="F28" s="6" t="inlineStr">
@@ -17058,7 +17058,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U28" s="7" t="inlineStr">
+      <c r="U28" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -17073,7 +17073,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="X28" s="7" t="inlineStr">
+      <c r="X28" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -17108,12 +17108,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE28" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF28" s="7" t="inlineStr">
+      <c r="AE28" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF28" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -17128,19 +17128,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI28" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AJ28" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AK28" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AI28" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AJ28" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AK28" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AL28" s="6" t="inlineStr">
@@ -17193,7 +17193,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AV28" s="7" t="inlineStr">
+      <c r="AV28" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -17203,17 +17203,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX28" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AY28" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AZ28" s="7" t="inlineStr">
+      <c r="AX28" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AY28" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AZ28" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -17228,9 +17228,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC28" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BC28" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -17255,9 +17255,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E29" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="F29" s="6" t="inlineStr">
@@ -17335,7 +17335,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U29" s="7" t="inlineStr">
+      <c r="U29" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -17350,7 +17350,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="X29" s="7" t="inlineStr">
+      <c r="X29" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -17385,12 +17385,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE29" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF29" s="7" t="inlineStr">
+      <c r="AE29" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF29" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -17405,19 +17405,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI29" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AJ29" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AK29" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AI29" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AJ29" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AK29" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AL29" s="6" t="inlineStr">
@@ -17470,7 +17470,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AV29" s="7" t="inlineStr">
+      <c r="AV29" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -17480,17 +17480,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX29" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AY29" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AZ29" s="7" t="inlineStr">
+      <c r="AX29" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AY29" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AZ29" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -17505,9 +17505,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC29" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BC29" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -17532,9 +17532,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E30" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="F30" s="6" t="inlineStr">
@@ -17612,7 +17612,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U30" s="7" t="inlineStr">
+      <c r="U30" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -17627,7 +17627,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="X30" s="7" t="inlineStr">
+      <c r="X30" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -17662,12 +17662,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE30" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF30" s="7" t="inlineStr">
+      <c r="AE30" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF30" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -17682,19 +17682,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI30" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AJ30" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AK30" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AI30" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AJ30" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AK30" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AL30" s="6" t="inlineStr">
@@ -17747,7 +17747,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AV30" s="7" t="inlineStr">
+      <c r="AV30" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -17757,17 +17757,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX30" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AY30" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AZ30" s="7" t="inlineStr">
+      <c r="AX30" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AY30" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AZ30" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -17782,9 +17782,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC30" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BC30" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -17809,9 +17809,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E31" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="F31" s="6" t="inlineStr">
@@ -17889,7 +17889,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U31" s="7" t="inlineStr">
+      <c r="U31" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -17904,7 +17904,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="X31" s="7" t="inlineStr">
+      <c r="X31" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -17939,12 +17939,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE31" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF31" s="7" t="inlineStr">
+      <c r="AE31" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF31" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -17959,19 +17959,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI31" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AJ31" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AK31" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AI31" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AJ31" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AK31" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AL31" s="6" t="inlineStr">
@@ -18024,7 +18024,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AV31" s="7" t="inlineStr">
+      <c r="AV31" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -18034,17 +18034,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX31" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AY31" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AZ31" s="7" t="inlineStr">
+      <c r="AX31" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AY31" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AZ31" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -18059,9 +18059,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC31" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BC31" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -18081,12 +18081,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D32" s="8" t="inlineStr">
+      <c r="D32" s="7" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="E32" s="8" t="inlineStr">
+      <c r="E32" s="7" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
@@ -18141,7 +18141,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="P32" s="7" t="inlineStr">
+      <c r="P32" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -18166,7 +18166,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U32" s="7" t="inlineStr">
+      <c r="U32" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -18181,7 +18181,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="X32" s="7" t="inlineStr">
+      <c r="X32" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -18216,12 +18216,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE32" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF32" s="7" t="inlineStr">
+      <c r="AE32" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF32" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -18236,17 +18236,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI32" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AJ32" s="8" t="inlineStr">
+      <c r="AI32" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AJ32" s="7" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AK32" s="8" t="inlineStr">
+      <c r="AK32" s="7" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
@@ -18301,7 +18301,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AV32" s="7" t="inlineStr">
+      <c r="AV32" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -18311,17 +18311,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX32" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AY32" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AZ32" s="7" t="inlineStr">
+      <c r="AX32" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AY32" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AZ32" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -18358,14 +18358,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D33" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="E33" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="F33" s="6" t="inlineStr">
@@ -18418,7 +18418,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="P33" s="7" t="inlineStr">
+      <c r="P33" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -18443,7 +18443,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U33" s="7" t="inlineStr">
+      <c r="U33" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -18458,7 +18458,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="X33" s="7" t="inlineStr">
+      <c r="X33" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -18493,12 +18493,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE33" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF33" s="7" t="inlineStr">
+      <c r="AE33" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF33" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -18513,19 +18513,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI33" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AJ33" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AK33" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AI33" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AJ33" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AK33" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AL33" s="6" t="inlineStr">
@@ -18578,7 +18578,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AV33" s="7" t="inlineStr">
+      <c r="AV33" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -18588,17 +18588,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX33" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AY33" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AZ33" s="7" t="inlineStr">
+      <c r="AX33" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AY33" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AZ33" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -18613,9 +18613,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC33" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BC33" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -18635,12 +18635,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D34" s="8" t="inlineStr">
+      <c r="D34" s="7" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="E34" s="8" t="inlineStr">
+      <c r="E34" s="7" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
@@ -18695,12 +18695,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="P34" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q34" s="7" t="inlineStr">
+      <c r="P34" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q34" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -18720,7 +18720,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U34" s="7" t="inlineStr">
+      <c r="U34" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -18735,7 +18735,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="X34" s="7" t="inlineStr">
+      <c r="X34" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -18770,12 +18770,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE34" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF34" s="7" t="inlineStr">
+      <c r="AE34" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF34" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -18790,17 +18790,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI34" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AJ34" s="8" t="inlineStr">
+      <c r="AI34" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AJ34" s="7" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AK34" s="8" t="inlineStr">
+      <c r="AK34" s="7" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
@@ -18820,12 +18820,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AO34" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AP34" s="7" t="inlineStr">
+      <c r="AO34" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AP34" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -18855,7 +18855,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AV34" s="7" t="inlineStr">
+      <c r="AV34" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -18865,17 +18865,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX34" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AY34" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AZ34" s="7" t="inlineStr">
+      <c r="AX34" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AY34" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AZ34" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -18912,14 +18912,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D35" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="E35" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="D35" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="F35" s="6" t="inlineStr">
@@ -18972,12 +18972,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="P35" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q35" s="7" t="inlineStr">
+      <c r="P35" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q35" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -18997,7 +18997,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U35" s="7" t="inlineStr">
+      <c r="U35" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -19012,7 +19012,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="X35" s="7" t="inlineStr">
+      <c r="X35" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -19047,12 +19047,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE35" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF35" s="7" t="inlineStr">
+      <c r="AE35" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF35" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -19067,19 +19067,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI35" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AJ35" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AK35" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AI35" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AJ35" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AK35" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AL35" s="6" t="inlineStr">
@@ -19097,12 +19097,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AO35" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AP35" s="7" t="inlineStr">
+      <c r="AO35" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AP35" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -19132,7 +19132,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AV35" s="7" t="inlineStr">
+      <c r="AV35" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -19142,17 +19142,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX35" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AY35" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AZ35" s="7" t="inlineStr">
+      <c r="AX35" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AY35" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AZ35" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -19167,9 +19167,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC35" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BC35" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -19194,9 +19194,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E36" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E36" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="F36" s="6" t="inlineStr">
@@ -19254,7 +19254,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Q36" s="7" t="inlineStr">
+      <c r="Q36" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -19274,7 +19274,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U36" s="7" t="inlineStr">
+      <c r="U36" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -19289,7 +19289,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="X36" s="7" t="inlineStr">
+      <c r="X36" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -19324,12 +19324,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE36" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF36" s="7" t="inlineStr">
+      <c r="AE36" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF36" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -19344,19 +19344,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI36" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AJ36" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AK36" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AI36" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AJ36" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AK36" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AL36" s="6" t="inlineStr">
@@ -19409,7 +19409,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AV36" s="7" t="inlineStr">
+      <c r="AV36" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -19419,17 +19419,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX36" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AY36" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AZ36" s="7" t="inlineStr">
+      <c r="AX36" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AY36" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AZ36" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -19444,9 +19444,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC36" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BC36" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -19471,9 +19471,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E37" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="F37" s="6" t="inlineStr">
@@ -19521,7 +19521,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O37" s="7" t="inlineStr">
+      <c r="O37" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -19531,7 +19531,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Q37" s="7" t="inlineStr">
+      <c r="Q37" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -19551,7 +19551,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U37" s="7" t="inlineStr">
+      <c r="U37" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -19566,7 +19566,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="X37" s="7" t="inlineStr">
+      <c r="X37" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -19601,12 +19601,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE37" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF37" s="7" t="inlineStr">
+      <c r="AE37" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF37" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -19621,19 +19621,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI37" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AJ37" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AK37" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AI37" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AJ37" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AK37" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AL37" s="6" t="inlineStr">
@@ -19651,12 +19651,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AO37" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AP37" s="7" t="inlineStr">
+      <c r="AO37" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AP37" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -19686,7 +19686,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AV37" s="7" t="inlineStr">
+      <c r="AV37" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -19696,17 +19696,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX37" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AY37" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AZ37" s="7" t="inlineStr">
+      <c r="AX37" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AY37" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AZ37" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -19721,9 +19721,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC37" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BC37" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -19748,7 +19748,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E38" s="8" t="inlineStr">
+      <c r="E38" s="7" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
@@ -19808,7 +19808,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Q38" s="7" t="inlineStr">
+      <c r="Q38" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -19828,7 +19828,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U38" s="7" t="inlineStr">
+      <c r="U38" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -19843,7 +19843,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="X38" s="7" t="inlineStr">
+      <c r="X38" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -19878,12 +19878,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE38" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF38" s="7" t="inlineStr">
+      <c r="AE38" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF38" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -19898,17 +19898,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI38" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AJ38" s="8" t="inlineStr">
+      <c r="AI38" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AJ38" s="7" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AK38" s="8" t="inlineStr">
+      <c r="AK38" s="7" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
@@ -19928,12 +19928,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AO38" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AP38" s="7" t="inlineStr">
+      <c r="AO38" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AP38" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -19963,7 +19963,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AV38" s="7" t="inlineStr">
+      <c r="AV38" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -19973,17 +19973,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX38" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AY38" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AZ38" s="7" t="inlineStr">
+      <c r="AX38" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AY38" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AZ38" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -20025,7 +20025,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E39" s="8" t="inlineStr">
+      <c r="E39" s="7" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
@@ -20085,7 +20085,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Q39" s="7" t="inlineStr">
+      <c r="Q39" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -20105,7 +20105,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U39" s="7" t="inlineStr">
+      <c r="U39" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -20120,7 +20120,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="X39" s="7" t="inlineStr">
+      <c r="X39" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -20155,12 +20155,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE39" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF39" s="7" t="inlineStr">
+      <c r="AE39" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF39" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -20175,17 +20175,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI39" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AJ39" s="8" t="inlineStr">
+      <c r="AI39" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AJ39" s="7" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AK39" s="8" t="inlineStr">
+      <c r="AK39" s="7" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
@@ -20240,7 +20240,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AV39" s="7" t="inlineStr">
+      <c r="AV39" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -20250,17 +20250,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX39" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AY39" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AZ39" s="7" t="inlineStr">
+      <c r="AX39" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AY39" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AZ39" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -20302,9 +20302,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E40" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E40" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="F40" s="6" t="inlineStr">
@@ -20362,7 +20362,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Q40" s="7" t="inlineStr">
+      <c r="Q40" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -20382,7 +20382,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U40" s="7" t="inlineStr">
+      <c r="U40" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -20397,7 +20397,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="X40" s="7" t="inlineStr">
+      <c r="X40" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -20432,12 +20432,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE40" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF40" s="7" t="inlineStr">
+      <c r="AE40" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF40" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -20452,19 +20452,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI40" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AJ40" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AK40" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AI40" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AJ40" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AK40" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AL40" s="6" t="inlineStr">
@@ -20517,7 +20517,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AV40" s="7" t="inlineStr">
+      <c r="AV40" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -20527,17 +20527,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX40" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AY40" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AZ40" s="7" t="inlineStr">
+      <c r="AX40" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AY40" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AZ40" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -20552,9 +20552,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC40" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BC40" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -20579,9 +20579,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E41" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E41" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="F41" s="6" t="inlineStr">
@@ -20639,7 +20639,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Q41" s="7" t="inlineStr">
+      <c r="Q41" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -20659,7 +20659,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U41" s="7" t="inlineStr">
+      <c r="U41" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -20674,7 +20674,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="X41" s="7" t="inlineStr">
+      <c r="X41" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -20709,12 +20709,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE41" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF41" s="7" t="inlineStr">
+      <c r="AE41" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF41" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -20729,19 +20729,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI41" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AJ41" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AK41" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AI41" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AJ41" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AK41" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AL41" s="6" t="inlineStr">
@@ -20794,7 +20794,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AV41" s="7" t="inlineStr">
+      <c r="AV41" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -20804,17 +20804,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX41" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AY41" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AZ41" s="7" t="inlineStr">
+      <c r="AX41" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AY41" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AZ41" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -20829,9 +20829,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC41" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BC41" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -20856,9 +20856,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E42" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E42" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="F42" s="6" t="inlineStr">
@@ -20916,7 +20916,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Q42" s="7" t="inlineStr">
+      <c r="Q42" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -20936,7 +20936,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U42" s="7" t="inlineStr">
+      <c r="U42" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -20951,7 +20951,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="X42" s="7" t="inlineStr">
+      <c r="X42" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -20986,12 +20986,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE42" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF42" s="7" t="inlineStr">
+      <c r="AE42" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF42" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -21006,19 +21006,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI42" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AJ42" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AK42" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AI42" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AJ42" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AK42" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AL42" s="6" t="inlineStr">
@@ -21071,7 +21071,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AV42" s="7" t="inlineStr">
+      <c r="AV42" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -21081,17 +21081,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX42" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AY42" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AZ42" s="7" t="inlineStr">
+      <c r="AX42" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AY42" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AZ42" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -21106,9 +21106,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC42" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BC42" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -21133,9 +21133,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E43" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E43" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="F43" s="6" t="inlineStr">
@@ -21193,7 +21193,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Q43" s="7" t="inlineStr">
+      <c r="Q43" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -21213,7 +21213,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U43" s="7" t="inlineStr">
+      <c r="U43" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -21228,7 +21228,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="X43" s="7" t="inlineStr">
+      <c r="X43" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -21263,12 +21263,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE43" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF43" s="7" t="inlineStr">
+      <c r="AE43" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF43" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -21283,19 +21283,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI43" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AJ43" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AK43" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AI43" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AJ43" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AK43" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AL43" s="6" t="inlineStr">
@@ -21348,7 +21348,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AV43" s="7" t="inlineStr">
+      <c r="AV43" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -21358,17 +21358,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX43" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AY43" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AZ43" s="7" t="inlineStr">
+      <c r="AX43" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AY43" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AZ43" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -21383,9 +21383,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC43" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BC43" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -21405,14 +21405,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D44" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="E44" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="D44" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="E44" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="F44" s="6" t="inlineStr">
@@ -21465,12 +21465,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="P44" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q44" s="7" t="inlineStr">
+      <c r="P44" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q44" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -21490,7 +21490,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U44" s="7" t="inlineStr">
+      <c r="U44" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -21505,7 +21505,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="X44" s="7" t="inlineStr">
+      <c r="X44" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -21540,12 +21540,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE44" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF44" s="7" t="inlineStr">
+      <c r="AE44" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF44" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -21560,19 +21560,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI44" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AJ44" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AK44" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AI44" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AJ44" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AK44" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AL44" s="6" t="inlineStr">
@@ -21625,7 +21625,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AV44" s="7" t="inlineStr">
+      <c r="AV44" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -21635,17 +21635,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX44" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AY44" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AZ44" s="7" t="inlineStr">
+      <c r="AX44" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AY44" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AZ44" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -21660,9 +21660,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC44" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BC44" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -21682,14 +21682,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D45" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="E45" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="D45" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="E45" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="F45" s="6" t="inlineStr">
@@ -21742,12 +21742,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="P45" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q45" s="7" t="inlineStr">
+      <c r="P45" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q45" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -21767,7 +21767,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U45" s="7" t="inlineStr">
+      <c r="U45" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -21782,7 +21782,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="X45" s="7" t="inlineStr">
+      <c r="X45" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -21817,12 +21817,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE45" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF45" s="7" t="inlineStr">
+      <c r="AE45" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF45" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -21837,19 +21837,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI45" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AJ45" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AK45" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AI45" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AJ45" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AK45" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AL45" s="6" t="inlineStr">
@@ -21902,7 +21902,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AV45" s="7" t="inlineStr">
+      <c r="AV45" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -21912,17 +21912,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX45" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AY45" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AZ45" s="7" t="inlineStr">
+      <c r="AX45" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AY45" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AZ45" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -21937,9 +21937,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC45" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BC45" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -21959,14 +21959,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D46" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="E46" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="D46" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="E46" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="F46" s="6" t="inlineStr">
@@ -22019,12 +22019,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="P46" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q46" s="7" t="inlineStr">
+      <c r="P46" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q46" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -22044,7 +22044,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U46" s="7" t="inlineStr">
+      <c r="U46" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -22059,7 +22059,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="X46" s="7" t="inlineStr">
+      <c r="X46" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -22094,12 +22094,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE46" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF46" s="7" t="inlineStr">
+      <c r="AE46" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF46" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -22114,19 +22114,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI46" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AJ46" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AK46" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AI46" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AJ46" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AK46" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AL46" s="6" t="inlineStr">
@@ -22144,12 +22144,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AO46" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AP46" s="7" t="inlineStr">
+      <c r="AO46" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AP46" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -22179,7 +22179,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AV46" s="7" t="inlineStr">
+      <c r="AV46" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -22189,17 +22189,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX46" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AY46" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AZ46" s="7" t="inlineStr">
+      <c r="AX46" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AY46" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AZ46" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -22214,9 +22214,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC46" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BC46" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -22236,14 +22236,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D47" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="E47" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="D47" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="E47" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="F47" s="6" t="inlineStr">
@@ -22296,12 +22296,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="P47" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q47" s="7" t="inlineStr">
+      <c r="P47" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q47" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -22321,7 +22321,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U47" s="7" t="inlineStr">
+      <c r="U47" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -22336,7 +22336,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="X47" s="7" t="inlineStr">
+      <c r="X47" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -22371,12 +22371,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE47" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF47" s="7" t="inlineStr">
+      <c r="AE47" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF47" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -22391,19 +22391,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI47" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AJ47" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AK47" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AI47" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AJ47" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AK47" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AL47" s="6" t="inlineStr">
@@ -22421,12 +22421,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AO47" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AP47" s="7" t="inlineStr">
+      <c r="AO47" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AP47" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -22456,7 +22456,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AV47" s="7" t="inlineStr">
+      <c r="AV47" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -22466,17 +22466,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX47" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AY47" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AZ47" s="7" t="inlineStr">
+      <c r="AX47" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AY47" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AZ47" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -22491,9 +22491,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC47" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BC47" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -22518,9 +22518,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E48" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E48" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="F48" s="6" t="inlineStr">
@@ -22598,7 +22598,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U48" s="7" t="inlineStr">
+      <c r="U48" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -22618,12 +22618,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Y48" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z48" s="7" t="inlineStr">
+      <c r="Y48" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z48" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -22648,12 +22648,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE48" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF48" s="7" t="inlineStr">
+      <c r="AE48" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF48" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -22668,19 +22668,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI48" s="7" t="inlineStr">
+      <c r="AI48" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AJ48" s="7" t="inlineStr">
         <is>
-          <t>UNAVAILABLE</t>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AK48" s="7" t="inlineStr">
         <is>
-          <t>UNAVAILABLE</t>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AL48" s="6" t="inlineStr">
@@ -22698,12 +22698,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AO48" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AP48" s="7" t="inlineStr">
+      <c r="AO48" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AP48" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -22733,7 +22733,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AV48" s="7" t="inlineStr">
+      <c r="AV48" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -22743,17 +22743,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX48" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AY48" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AZ48" s="7" t="inlineStr">
+      <c r="AX48" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AY48" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AZ48" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -22768,9 +22768,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC48" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BC48" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -22795,9 +22795,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E49" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E49" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="F49" s="6" t="inlineStr">
@@ -22875,7 +22875,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U49" s="7" t="inlineStr">
+      <c r="U49" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -22895,12 +22895,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Y49" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z49" s="7" t="inlineStr">
+      <c r="Y49" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z49" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -22925,12 +22925,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE49" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF49" s="7" t="inlineStr">
+      <c r="AE49" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF49" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -22945,19 +22945,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI49" s="7" t="inlineStr">
+      <c r="AI49" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AJ49" s="7" t="inlineStr">
         <is>
-          <t>UNAVAILABLE</t>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AK49" s="7" t="inlineStr">
         <is>
-          <t>UNAVAILABLE</t>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AL49" s="6" t="inlineStr">
@@ -23000,7 +23000,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT49" s="7" t="inlineStr">
+      <c r="AT49" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -23010,7 +23010,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AV49" s="7" t="inlineStr">
+      <c r="AV49" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -23020,17 +23020,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX49" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AY49" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AZ49" s="7" t="inlineStr">
+      <c r="AX49" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AY49" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AZ49" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -23045,9 +23045,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC49" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BC49" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -23072,9 +23072,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E50" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E50" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="F50" s="6" t="inlineStr">
@@ -23152,7 +23152,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U50" s="7" t="inlineStr">
+      <c r="U50" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -23172,12 +23172,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Y50" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z50" s="7" t="inlineStr">
+      <c r="Y50" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z50" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -23202,12 +23202,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE50" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF50" s="7" t="inlineStr">
+      <c r="AE50" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF50" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -23222,19 +23222,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI50" s="7" t="inlineStr">
+      <c r="AI50" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AJ50" s="7" t="inlineStr">
         <is>
-          <t>UNAVAILABLE</t>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AK50" s="7" t="inlineStr">
         <is>
-          <t>UNAVAILABLE</t>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AL50" s="6" t="inlineStr">
@@ -23252,12 +23252,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AO50" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AP50" s="7" t="inlineStr">
+      <c r="AO50" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AP50" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -23287,7 +23287,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AV50" s="7" t="inlineStr">
+      <c r="AV50" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -23297,17 +23297,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX50" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AY50" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AZ50" s="7" t="inlineStr">
+      <c r="AX50" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AY50" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AZ50" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -23322,9 +23322,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC50" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BC50" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -23349,9 +23349,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E51" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E51" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="F51" s="6" t="inlineStr">
@@ -23429,7 +23429,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U51" s="7" t="inlineStr">
+      <c r="U51" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -23449,12 +23449,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Y51" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z51" s="7" t="inlineStr">
+      <c r="Y51" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z51" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -23479,12 +23479,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE51" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF51" s="7" t="inlineStr">
+      <c r="AE51" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF51" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -23499,19 +23499,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI51" s="7" t="inlineStr">
+      <c r="AI51" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AJ51" s="7" t="inlineStr">
         <is>
-          <t>UNAVAILABLE</t>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AK51" s="7" t="inlineStr">
         <is>
-          <t>UNAVAILABLE</t>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AL51" s="6" t="inlineStr">
@@ -23564,7 +23564,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AV51" s="7" t="inlineStr">
+      <c r="AV51" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -23574,17 +23574,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX51" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AY51" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AZ51" s="7" t="inlineStr">
+      <c r="AX51" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AY51" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AZ51" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -23599,9 +23599,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC51" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BC51" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -23620,7 +23620,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -23654,12 +23654,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>STM32MP251A</t>
+          <t>STM32MP215D</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -23669,19 +23669,19 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>cover names Arm Cortex-A35, Arm Cortex-M33, Arm Cortex-M0+; ST reports the application core here and the others as co-processors</t>
+          <t>Table 1. STM32MP21xA/D features and peripheral counts lists VFBGA225 (8x8 pitch 0.5 mm), VFBGA273 (11x11 pitch 0.5 mm) for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>STM32MP251A</t>
+          <t>STM32MP215D</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -23691,19 +23691,19 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>cover names Arm Cortex-A35, Arm Cortex-M33; ST reports the application core here and the others as co-processors</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>STM32MP251A</t>
+          <t>STM32MP215D</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -23720,12 +23720,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>STM32MP251C</t>
+          <t>STM32MP215D</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -23735,19 +23735,19 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>cover names Arm Cortex-A35, Arm Cortex-M33, Arm Cortex-M0+; ST reports the application core here and the others as co-processors</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>STM32MP251C</t>
+          <t>STM32MP215F</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -23757,19 +23757,19 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 1. STM32MP21xC/F features and peripheral counts lists TFBGA289 (14x14 pitch 0.8 mm), VFBGA225 (8x8 pitch 0.5 mm), VFBGA273 (11x11 pitch 0.5 mm), VFBGA361 (10x10 pitch 0.5 mm) for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>STM32MP251C</t>
+          <t>STM32MP215F</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -23779,19 +23779,19 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>cover names Arm Cortex-A35, Arm Cortex-M33; ST reports the application core here and the others as co-processors</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>STM32MP211C</t>
+          <t>STM32MP215F</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -23801,19 +23801,19 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Table 1. STM32MP21xC/F features and peripheral counts lists TFBGA289 (14x14 pitch 0.8 mm), VFBGA225 (8x8 pitch 0.5 mm), VFBGA273 (11x11 pitch 0.5 mm), VFBGA361 (10x10 pitch 0.5 mm) for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 0), and the table does not say which timers the variant omits</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>STM32MP211C</t>
+          <t>STM32MP215F</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -23823,19 +23823,19 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>cover names Arm Cortex-A35, Arm Cortex-M33; ST reports the application core here and the others as co-processors</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 0), and the table does not say which timers the variant omits</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>STM32MP211C</t>
+          <t>STM32MP215A</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -23845,19 +23845,19 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 0), and the table does not say which timers the variant omits</t>
+          <t>Table 1. STM32MP21xA/D features and peripheral counts lists VFBGA225 (8x8 pitch 0.5 mm), VFBGA273 (11x11 pitch 0.5 mm) for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>STM32MP211C</t>
+          <t>STM32MP215A</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -23867,19 +23867,19 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 0), and the table does not say which timers the variant omits</t>
+          <t>cover names Arm Cortex-A35, Arm Cortex-M33; ST reports the application core here and the others as co-processors</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>STM32MP211A</t>
+          <t>STM32MP215A</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -23889,19 +23889,19 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Table 1. STM32MP21xA/D features and peripheral counts lists VFBGA225 (8x8 pitch 0.5 mm), VFBGA273 (11x11 pitch 0.5 mm) for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>STM32MP211A</t>
+          <t>STM32MP215A</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -23911,19 +23911,19 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>cover names Arm Cortex-A35, Arm Cortex-M33; ST reports the application core here and the others as co-processors</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>STM32MP211A</t>
+          <t>STM32MP215C</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -23933,19 +23933,19 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 1. STM32MP21xC/F features and peripheral counts lists TFBGA289 (14x14 pitch 0.8 mm), VFBGA225 (8x8 pitch 0.5 mm), VFBGA273 (11x11 pitch 0.5 mm), VFBGA361 (10x10 pitch 0.5 mm) for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>STM32MP211A</t>
+          <t>STM32MP215C</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -23955,19 +23955,19 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>cover names Arm Cortex-A35, Arm Cortex-M33; ST reports the application core here and the others as co-processors</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>STM32MP231A</t>
+          <t>STM32MP215C</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -23977,19 +23977,19 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>cover names Arm Cortex-A35, Arm Cortex-M33; ST reports the application core here and the others as co-processors</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 0), and the table does not say which timers the variant omits</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>STM32MP231A</t>
+          <t>STM32MP215C</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -23999,19 +23999,19 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 0), and the table does not say which timers the variant omits</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>STM32MP231A</t>
+          <t>STM32MP255F</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -24021,19 +24021,19 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>cover names Arm Cortex-A35, Arm Cortex-M33, Arm Cortex-M0+; ST reports the application core here and the others as co-processors</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>STM32MP231C</t>
+          <t>STM32MP255F</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -24043,19 +24043,19 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>cover names Arm Cortex-A35, Arm Cortex-M33; ST reports the application core here and the others as co-processors</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>STM32MP231C</t>
+          <t>STM32MP255F</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -24072,20 +24072,2484 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>STM32MP255A</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>cover names Arm Cortex-A35, Arm Cortex-M33, Arm Cortex-M0+; ST reports the application core here and the others as co-processors</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>STM32MP255A</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>STM32MP255A</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>STM32MP255C</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>cover names Arm Cortex-A35, Arm Cortex-M33, Arm Cortex-M0+; ST reports the application core here and the others as co-processors</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>STM32MP255C</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>STM32MP255C</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>STM32MP255D</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>cover names Arm Cortex-A35, Arm Cortex-M33, Arm Cortex-M0+; ST reports the application core here and the others as co-processors</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>STM32MP255D</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>STM32MP255D</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>STM32MP251A</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>cover names Arm Cortex-A35, Arm Cortex-M33, Arm Cortex-M0+; ST reports the application core here and the others as co-processors</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>STM32MP251A</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>STM32MP251A</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>STM32MP251C</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>cover names Arm Cortex-A35, Arm Cortex-M33, Arm Cortex-M0+; ST reports the application core here and the others as co-processors</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>STM32MP251C</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>STM32MP251C</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>STM32MP251D</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>cover names Arm Cortex-A35, Arm Cortex-M33, Arm Cortex-M0+; ST reports the application core here and the others as co-processors</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>STM32MP251D</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>STM32MP251D</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>STM32MP251F</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>cover names Arm Cortex-A35, Arm Cortex-M33, Arm Cortex-M0+; ST reports the application core here and the others as co-processors</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>STM32MP251F</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>STM32MP251F</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>STM32MP253F</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>cover names Arm Cortex-A35, Arm Cortex-M33, Arm Cortex-M0+; ST reports the application core here and the others as co-processors</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>STM32MP253F</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>STM32MP253F</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>STM32MP253A</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>cover names Arm Cortex-A35, Arm Cortex-M33, Arm Cortex-M0+; ST reports the application core here and the others as co-processors</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>STM32MP253A</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>STM32MP253A</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>STM32MP253C</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>cover names Arm Cortex-A35, Arm Cortex-M33, Arm Cortex-M0+; ST reports the application core here and the others as co-processors</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>STM32MP253C</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>STM32MP253C</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>STM32MP253D</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>cover names Arm Cortex-A35, Arm Cortex-M33, Arm Cortex-M0+; ST reports the application core here and the others as co-processors</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>STM32MP253D</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>STM32MP253D</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>STM32MP235C</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>cover names Arm Cortex-A35, Arm Cortex-M33; ST reports the application core here and the others as co-processors</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>STM32MP235C</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>STM32MP235C</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>STM32MP235A</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>cover names Arm Cortex-A35, Arm Cortex-M33; ST reports the application core here and the others as co-processors</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>STM32MP235A</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>STM32MP235A</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>STM32MP235D</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>cover names Arm Cortex-A35, Arm Cortex-M33; ST reports the application core here and the others as co-processors</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>STM32MP235D</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>STM32MP235D</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>STM32MP235F</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>cover names Arm Cortex-A35, Arm Cortex-M33; ST reports the application core here and the others as co-processors</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>STM32MP235F</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>STM32MP235F</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>STM32MP211C</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Table 1. STM32MP21xC/F features and peripheral counts lists TFBGA289 (14x14 pitch 0.8 mm), VFBGA225 (8x8 pitch 0.5 mm), VFBGA273 (11x11 pitch 0.5 mm), VFBGA361 (10x10 pitch 0.5 mm) for this family; the table gives no key to tie a package to this part</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>STM32MP211C</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>cover names Arm Cortex-A35, Arm Cortex-M33; ST reports the application core here and the others as co-processors</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>STM32MP211C</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 0), and the table does not say which timers the variant omits</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>STM32MP211C</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 0), and the table does not say which timers the variant omits</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>STM32MP211F</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Table 1. STM32MP21xC/F features and peripheral counts lists TFBGA289 (14x14 pitch 0.8 mm), VFBGA225 (8x8 pitch 0.5 mm), VFBGA273 (11x11 pitch 0.5 mm), VFBGA361 (10x10 pitch 0.5 mm) for this family; the table gives no key to tie a package to this part</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>STM32MP211F</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>cover names Arm Cortex-A35, Arm Cortex-M33; ST reports the application core here and the others as co-processors</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>STM32MP211F</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 0), and the table does not say which timers the variant omits</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>STM32MP211F</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 0), and the table does not say which timers the variant omits</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>STM32MP211A</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Table 1. STM32MP21xA/D features and peripheral counts lists VFBGA225 (8x8 pitch 0.5 mm), VFBGA273 (11x11 pitch 0.5 mm) for this family; the table gives no key to tie a package to this part</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>STM32MP211A</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>cover names Arm Cortex-A35, Arm Cortex-M33; ST reports the application core here and the others as co-processors</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>STM32MP211A</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>STM32MP211A</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>STM32MP211D</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Table 1. STM32MP21xA/D features and peripheral counts lists VFBGA225 (8x8 pitch 0.5 mm), VFBGA273 (11x11 pitch 0.5 mm) for this family; the table gives no key to tie a package to this part</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>STM32MP211D</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>cover names Arm Cortex-A35, Arm Cortex-M33; ST reports the application core here and the others as co-processors</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>STM32MP211D</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>STM32MP211D</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>STM32MP231F</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>cover names Arm Cortex-A35, Arm Cortex-M33; ST reports the application core here and the others as co-processors</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>STM32MP231F</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>STM32MP231F</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>STM32MP231D</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>cover names Arm Cortex-A35, Arm Cortex-M33; ST reports the application core here and the others as co-processors</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>STM32MP231D</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>STM32MP231D</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>STM32MP231A</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>cover names Arm Cortex-A35, Arm Cortex-M33; ST reports the application core here and the others as co-processors</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>STM32MP231A</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>STM32MP231A</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
           <t>STM32MP231C</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>cover names Arm Cortex-A35, Arm Cortex-M33; ST reports the application core here and the others as co-processors</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>STM32MP231C</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>STM32MP231C</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
         <is>
           <t>Timers (32-bit) typ</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C93" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>STM32MP233C</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>cover names Arm Cortex-A35, Arm Cortex-M33; ST reports the application core here and the others as co-processors</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>STM32MP233C</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>STM32MP233C</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>STM32MP233F</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>cover names Arm Cortex-A35, Arm Cortex-M33; ST reports the application core here and the others as co-processors</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>STM32MP233F</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>STM32MP233F</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>STM32MP233A</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>cover names Arm Cortex-A35, Arm Cortex-M33; ST reports the application core here and the others as co-processors</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>STM32MP233A</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>STM32MP233A</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>STM32MP233D</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>cover names Arm Cortex-A35, Arm Cortex-M33; ST reports the application core here and the others as co-processors</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>STM32MP233D</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>STM32MP233D</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>STM32MP213C</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Table 1. STM32MP21xC/F features and peripheral counts lists TFBGA289 (14x14 pitch 0.8 mm), VFBGA225 (8x8 pitch 0.5 mm), VFBGA273 (11x11 pitch 0.5 mm), VFBGA361 (10x10 pitch 0.5 mm) for this family; the table gives no key to tie a package to this part</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>STM32MP213C</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>cover names Arm Cortex-A35, Arm Cortex-M33; ST reports the application core here and the others as co-processors</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>STM32MP213C</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 0), and the table does not say which timers the variant omits</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>STM32MP213C</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 0), and the table does not say which timers the variant omits</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>STM32MP213F</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Table 1. STM32MP21xC/F features and peripheral counts lists TFBGA289 (14x14 pitch 0.8 mm), VFBGA225 (8x8 pitch 0.5 mm), VFBGA273 (11x11 pitch 0.5 mm), VFBGA361 (10x10 pitch 0.5 mm) for this family; the table gives no key to tie a package to this part</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>STM32MP213F</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>cover names Arm Cortex-A35, Arm Cortex-M33; ST reports the application core here and the others as co-processors</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>STM32MP213F</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 0), and the table does not say which timers the variant omits</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>STM32MP213F</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 0), and the table does not say which timers the variant omits</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>STM32MP213A</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Table 1. STM32MP21xA/D features and peripheral counts lists VFBGA225 (8x8 pitch 0.5 mm), VFBGA273 (11x11 pitch 0.5 mm) for this family; the table gives no key to tie a package to this part</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>STM32MP213A</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>cover names Arm Cortex-A35, Arm Cortex-M33; ST reports the application core here and the others as co-processors</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>STM32MP213A</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>STM32MP213A</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>STM32MP213D</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Table 1. STM32MP21xA/D features and peripheral counts lists VFBGA225 (8x8 pitch 0.5 mm), VFBGA273 (11x11 pitch 0.5 mm) for this family; the table gives no key to tie a package to this part</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>STM32MP213D</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>cover names Arm Cortex-A35, Arm Cortex-M33; ST reports the application core here and the others as co-processors</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>STM32MP213D</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>STM32MP213D</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>STM32MP257A</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>cover names Arm Cortex-A35, Arm Cortex-M33, Arm Cortex-M0+; ST reports the application core here and the others as co-processors</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>STM32MP257A</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>STM32MP257A</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>STM32MP257C</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>cover names Arm Cortex-A35, Arm Cortex-M33, Arm Cortex-M0+; ST reports the application core here and the others as co-processors</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>STM32MP257C</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>STM32MP257C</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>STM32MP257D</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>cover names Arm Cortex-A35, Arm Cortex-M33, Arm Cortex-M0+; ST reports the application core here and the others as co-processors</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>STM32MP257D</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>STM32MP257D</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>STM32MP257F</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>cover names Arm Cortex-A35, Arm Cortex-M33, Arm Cortex-M0+; ST reports the application core here and the others as co-processors</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>STM32MP257F</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>STM32MP257F</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
         <is>
           <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>

--- a/product_selector_out/STM32MP2 series.xlsx
+++ b/product_selector_out/STM32MP2 series.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BC51"/>
+  <dimension ref="A1:BD51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.828125" customWidth="1" min="1" max="1"/>
@@ -551,7 +551,8 @@
     <col width="18" customWidth="1" min="52" max="52"/>
     <col width="18" customWidth="1" min="53" max="53"/>
     <col width="18" customWidth="1" min="54" max="54"/>
-    <col width="52" customWidth="1" min="55" max="55"/>
+    <col width="18" customWidth="1" min="55" max="55"/>
+    <col width="52" customWidth="1" min="56" max="56"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -833,6 +834,11 @@
         </is>
       </c>
       <c r="BC10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BD10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -910,6 +916,7 @@
       <c r="BA11" s="2" t="n"/>
       <c r="BB11" s="2" t="n"/>
       <c r="BC11" s="2" t="n"/>
+      <c r="BD11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -1187,6 +1194,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BD12" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -1464,6 +1476,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BD13" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -1741,6 +1758,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BD14" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -2018,6 +2040,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BD15" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
@@ -2295,6 +2322,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BD16" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
@@ -2572,6 +2604,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BD17" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
@@ -2849,6 +2886,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BD18" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
@@ -3126,6 +3168,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BD19" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
@@ -3400,6 +3447,11 @@
       </c>
       <c r="BC20" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BD20" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32mp251a.pdf</t>
         </is>
       </c>
@@ -3677,6 +3729,11 @@
       </c>
       <c r="BC21" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BD21" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32mp251c.pdf</t>
         </is>
       </c>
@@ -3957,6 +4014,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BD22" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
@@ -4234,6 +4296,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BD23" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
@@ -4511,6 +4578,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BD24" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
@@ -4788,6 +4860,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BD25" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
@@ -5065,6 +5142,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BD26" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
@@ -5342,6 +5424,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BD27" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
@@ -5619,6 +5706,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BD28" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
@@ -5896,6 +5988,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BD29" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
@@ -6173,6 +6270,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BD30" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
@@ -6450,6 +6552,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BD31" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
@@ -6724,6 +6831,11 @@
       </c>
       <c r="BC32" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BD32" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32mp211c.pdf</t>
         </is>
       </c>
@@ -7004,6 +7116,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BD33" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
@@ -7278,6 +7395,11 @@
       </c>
       <c r="BC34" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BD34" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32mp211a.pdf</t>
         </is>
       </c>
@@ -7558,6 +7680,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BD35" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
@@ -7835,6 +7962,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BD36" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
@@ -8112,6 +8244,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BD37" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
@@ -8386,6 +8523,11 @@
       </c>
       <c r="BC38" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BD38" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32mp231a.pdf</t>
         </is>
       </c>
@@ -8663,6 +8805,11 @@
       </c>
       <c r="BC39" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BD39" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32mp231c.pdf</t>
         </is>
       </c>
@@ -8943,6 +9090,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BD40" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
@@ -9220,6 +9372,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BD41" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
@@ -9497,6 +9654,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BD42" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
@@ -9774,6 +9936,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BD43" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
@@ -10051,6 +10218,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BD44" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
@@ -10328,6 +10500,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BD45" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
@@ -10605,6 +10782,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BD46" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
@@ -10882,6 +11064,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BD47" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
@@ -11159,6 +11346,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BD48" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
@@ -11436,6 +11628,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BD49" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
@@ -11713,6 +11910,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BD50" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
@@ -11990,9 +12192,14 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BD51" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="55">
+  <mergeCells count="56">
     <mergeCell ref="P10:P11"/>
     <mergeCell ref="AS10:AS11"/>
     <mergeCell ref="AD10:AD11"/>
@@ -12005,16 +12212,18 @@
     <mergeCell ref="V10:V11"/>
     <mergeCell ref="G10:G11"/>
     <mergeCell ref="M10:M11"/>
+    <mergeCell ref="A9:BD9"/>
+    <mergeCell ref="A1:BD8"/>
+    <mergeCell ref="Y10:Y11"/>
     <mergeCell ref="AJ10:AJ11"/>
-    <mergeCell ref="Y10:Y11"/>
+    <mergeCell ref="Q10:Q11"/>
     <mergeCell ref="AP10:AP11"/>
-    <mergeCell ref="BA10:BA11"/>
-    <mergeCell ref="Q10:Q11"/>
     <mergeCell ref="AR10:AR11"/>
+    <mergeCell ref="S10:S11"/>
     <mergeCell ref="AT10:AT11"/>
-    <mergeCell ref="S10:S11"/>
     <mergeCell ref="AV10:AV11"/>
     <mergeCell ref="BB10:BB11"/>
+    <mergeCell ref="BD10:BD11"/>
     <mergeCell ref="AC10:AC11"/>
     <mergeCell ref="B10:B11"/>
     <mergeCell ref="AK10:AK11"/>
@@ -12026,9 +12235,8 @@
     <mergeCell ref="Z10:Z11"/>
     <mergeCell ref="AQ10:AQ11"/>
     <mergeCell ref="AW10:AW11"/>
-    <mergeCell ref="A1:BC8"/>
     <mergeCell ref="AY10:AY11"/>
-    <mergeCell ref="A9:BC9"/>
+    <mergeCell ref="BA10:BA11"/>
     <mergeCell ref="AE10:AF10"/>
     <mergeCell ref="A10:A11"/>
     <mergeCell ref="I10:I11"/>
@@ -12102,7 +12310,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BC51"/>
+  <dimension ref="A1:BD51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -12160,6 +12368,7 @@
     <col width="16" customWidth="1" min="53" max="53"/>
     <col width="16" customWidth="1" min="54" max="54"/>
     <col width="16" customWidth="1" min="55" max="55"/>
+    <col width="16" customWidth="1" min="56" max="56"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -12447,6 +12656,11 @@
         </is>
       </c>
       <c r="BC10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BD10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -12524,6 +12738,7 @@
       <c r="BA11" s="2" t="n"/>
       <c r="BB11" s="2" t="n"/>
       <c r="BC11" s="2" t="n"/>
+      <c r="BD11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -12801,6 +13016,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BD12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
@@ -13078,6 +13298,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BD13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
@@ -13355,6 +13580,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BD14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
@@ -13632,6 +13862,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BD15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
@@ -13909,6 +14144,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BD16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
@@ -14186,6 +14426,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BD17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
@@ -14463,6 +14708,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BD18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
@@ -14740,6 +14990,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BD19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
@@ -15012,7 +15267,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC20" s="6" t="inlineStr">
+      <c r="BC20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD20" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -15289,7 +15549,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC21" s="6" t="inlineStr">
+      <c r="BC21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD21" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -15571,6 +15836,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BD22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
@@ -15848,6 +16118,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BD23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
@@ -16125,6 +16400,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BD24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
@@ -16402,6 +16682,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BD25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
@@ -16679,6 +16964,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BD26" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
@@ -16956,6 +17246,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BD27" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
@@ -17233,6 +17528,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BD28" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
@@ -17510,6 +17810,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BD29" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
@@ -17787,6 +18092,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BD30" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
@@ -18064,6 +18374,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BD31" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
@@ -18336,7 +18651,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC32" s="6" t="inlineStr">
+      <c r="BC32" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD32" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -18618,6 +18938,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BD33" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
@@ -18890,7 +19215,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC34" s="6" t="inlineStr">
+      <c r="BC34" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD34" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -19172,6 +19502,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BD35" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
@@ -19449,6 +19784,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BD36" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
@@ -19726,6 +20066,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BD37" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
@@ -19998,7 +20343,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC38" s="6" t="inlineStr">
+      <c r="BC38" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD38" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -20275,7 +20625,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC39" s="6" t="inlineStr">
+      <c r="BC39" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD39" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -20557,6 +20912,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BD40" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
@@ -20834,6 +21194,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BD41" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
@@ -21111,6 +21476,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BD42" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
@@ -21388,6 +21758,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BD43" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
@@ -21665,6 +22040,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BD44" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
@@ -21942,6 +22322,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BD45" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
@@ -22219,6 +22604,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BD46" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
@@ -22496,6 +22886,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BD47" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
@@ -22773,6 +23168,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BD48" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
@@ -23050,6 +23450,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BD49" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
@@ -23327,6 +23732,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BD50" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
@@ -23604,11 +24014,16 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BD51" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A9:BC9"/>
-    <mergeCell ref="A1:BC8"/>
+    <mergeCell ref="A9:BD9"/>
+    <mergeCell ref="A1:BD8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
